--- a/Proyectos/PEPI/MODELO FINANCIERO PEPI (4).xlsx
+++ b/Proyectos/PEPI/MODELO FINANCIERO PEPI (4).xlsx
@@ -4,37 +4,41 @@
   <ns0:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <ns0:workbookPr/>
   <ns0:bookViews>
-    <ns0:workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" firstSheet="10" activeTab="10"/>
+    <ns0:workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" firstSheet="12" activeTab="12"/>
   </ns0:bookViews>
   <ns0:sheets>
     <ns0:sheet name="Control" sheetId="1" ns2:id="rId1"/>
     <ns0:sheet name="Supuestos" sheetId="2" ns2:id="rId2"/>
     <ns0:sheet name="Diseno Caudal" sheetId="3" ns2:id="rId3"/>
-    <ns0:sheet name="Presupuesto" sheetId="4" ns2:id="rId4"/>
-    <ns0:sheet name="Financiacion" sheetId="5" ns2:id="rId5"/>
-    <ns0:sheet name="Amortizacion Deuda" sheetId="6" ns2:id="rId6"/>
-    <ns0:sheet name="Flujos de Caja" sheetId="7" ns2:id="rId7"/>
-    <ns0:sheet name="Sensibilidad" sheetId="8" ns2:id="rId8"/>
-    <ns0:sheet name="Indicadores" sheetId="9" ns2:id="rId9"/>
-    <ns0:sheet name="Riesgos" sheetId="10" ns2:id="rId10"/>
+    <ns0:sheet name="APU Referencial" sheetId="4" ns2:id="rId4"/>
+    <ns0:sheet name="Fuentes" sheetId="5" ns2:id="rId5"/>
+    <ns0:sheet name="Presupuesto" sheetId="6" ns2:id="rId6"/>
+    <ns0:sheet name="Financiacion" sheetId="7" ns2:id="rId7"/>
+    <ns0:sheet name="Amortizacion Deuda" sheetId="8" ns2:id="rId8"/>
+    <ns0:sheet name="Flujos de Caja" sheetId="9" ns2:id="rId9"/>
+    <ns0:sheet name="Sensibilidad" sheetId="10" ns2:id="rId10"/>
+    <ns0:sheet name="Indicadores" sheetId="11" ns2:id="rId11"/>
+    <ns0:sheet name="Riesgos" sheetId="12" ns2:id="rId12"/>
   </ns0:sheets>
   <ns0:definedNames>
     <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supuestos'!$A$2:$D$2</ns0:definedName>
     <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Diseno Caudal'!$A$2:$C$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Presupuesto'!$A$2:$C$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Financiacion'!$A$2:$E$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Amortizacion Deuda'!$A$2:$F$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Flujos de Caja'!$A$2:$P$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sensibilidad'!$A$2:$AF$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Indicadores'!$A$2:$D$2</ns0:definedName>
-    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Riesgos'!$A$2:$H$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'APU Referencial'!$A$2:$N$44</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fuentes'!$A$2:$E$26</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Presupuesto'!$A$2:$C$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Financiacion'!$A$2:$E$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Amortizacion Deuda'!$A$2:$F$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Flujos de Caja'!$A$2:$P$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Sensibilidad'!$A$2:$AF$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Indicadores'!$A$2:$D$2</ns0:definedName>
+    <ns0:definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Riesgos'!$A$2:$H$2</ns0:definedName>
   </ns0:definedNames>
-  <ns0:calcPr fullCalcOnLoad="1"/>
+  <ns0:calcPr fullCalcOnLoad="1" calcMode="auto" forceFullCalc="1"/>
 </ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="671">
   <si>
     <t>MATRIZ 20 RIESGOS E INTERVENCIÓN 10 (5 AMBIENTALES)</t>
   </si>
@@ -558,6 +562,1107 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>Nota: el CAPEX ahora se obtiene del APU referencial. Las cantidades, rendimientos, componentes y AIU no proceden de diseños, SECOP ni cotizaciones; deben reemplazarse antes de cualquier uso contractual.</t>
+  </si>
+  <si>
+    <t>TRAZABILIDAD DE DATOS, FUENTES Y SUPUESTOS</t>
+  </si>
+  <si>
+    <t>Elemento</t>
+  </si>
+  <si>
+    <t>Dato usado</t>
+  </si>
+  <si>
+    <t>Procedencia declarada</t>
+  </si>
+  <si>
+    <t>Nivel de soporte / observación</t>
+  </si>
+  <si>
+    <t>¿Fuente verificable adjunta?</t>
+  </si>
+  <si>
+    <t>Enunciado y entregables</t>
+  </si>
+  <si>
+    <t>Estructura, matrices y límite de 10 páginas</t>
+  </si>
+  <si>
+    <t>PROYECTO PEPI.pdf suministrado en el repositorio</t>
+  </si>
+  <si>
+    <t>Fuente primaria del encargo</t>
+  </si>
+  <si>
+    <t>Sí — archivo adjunto</t>
+  </si>
+  <si>
+    <t>Caso de estudio</t>
+  </si>
+  <si>
+    <t>Optimización/ampliación del acueducto de Tadó, Chocó</t>
+  </si>
+  <si>
+    <t>Informe previo suministrado; atribuía el caso a MinVivienda, cooperación española y una nota de Agencia Anadolu sin título, fecha ni URL</t>
+  </si>
+  <si>
+    <t>Caso académico inspirado en una referencia secundaria no verificada</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Inversión ancla</t>
+  </si>
+  <si>
+    <t>COP 19.971 MM</t>
+  </si>
+  <si>
+    <t>Informe y modelo anteriores; atribuían el dato a la misma referencia secundaria no recuperable</t>
+  </si>
+  <si>
+    <t>No es presupuesto contractual ni APU oficial</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Población municipal</t>
+  </si>
+  <si>
+    <t>≈17.000 habitantes</t>
+  </si>
+  <si>
+    <t>Atribuida en el informe previo a DANE, CNPV 2018, consulta municipal de Tadó</t>
+  </si>
+  <si>
+    <t>Referencia identificada pero no adjunta; validar cifra exacta</t>
+  </si>
+  <si>
+    <t>No — referencia no adjunta</t>
+  </si>
+  <si>
+    <t>Población urbana base</t>
+  </si>
+  <si>
+    <t>10.957 habitantes</t>
+  </si>
+  <si>
+    <t>Entrada heredada del modelo anterior</t>
+  </si>
+  <si>
+    <t>No había soporte adjunto en el repositorio</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Crecimiento poblacional</t>
+  </si>
+  <si>
+    <t>1,2 % anual</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo</t>
+  </si>
+  <si>
+    <t>Debe reemplazarse con proyección oficial</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Horizonte de diseño</t>
+  </si>
+  <si>
+    <t>25 años</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo</t>
+  </si>
+  <si>
+    <t>No había memoria de selección adjunta</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Criterios hidráulicos</t>
+  </si>
+  <si>
+    <t>Dotación 140; pérdidas 25 %; k1=1,30; k2=1,60</t>
+  </si>
+  <si>
+    <t>Parámetros adoptados con referencia general a Resolución 0330 de 2017 — RAS</t>
+  </si>
+  <si>
+    <t>La norma no está adjunta; confirmar valores y aplicabilidad</t>
+  </si>
+  <si>
+    <t>No — referencia no adjunta</t>
+  </si>
+  <si>
+    <t>Capacidad PTAP</t>
+  </si>
+  <si>
+    <t>45 L/s</t>
+  </si>
+  <si>
+    <t>Alcance heredado del informe/modelo anterior</t>
+  </si>
+  <si>
+    <t>No hay diseño, balance horario ni ficha técnica adjunta</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Calidad de agua</t>
+  </si>
+  <si>
+    <t>IRCA y criterios de potabilidad</t>
+  </si>
+  <si>
+    <t>Resolución 2115 de 2007</t>
+  </si>
+  <si>
+    <t>Referencia normativa identificada pero no adjunta</t>
+  </si>
+  <si>
+    <t>No — referencia no adjunta</t>
+  </si>
+  <si>
+    <t>Marco tarifario</t>
+  </si>
+  <si>
+    <t>Estructura tarifaria del servicio</t>
+  </si>
+  <si>
+    <t>Resolución CRA 943 de 2021</t>
+  </si>
+  <si>
+    <t>Referencia normativa identificada pero no adjunta</t>
+  </si>
+  <si>
+    <t>No — referencia no adjunta</t>
+  </si>
+  <si>
+    <t>Horizonte de evaluación</t>
+  </si>
+  <si>
+    <t>25 años</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo</t>
+  </si>
+  <si>
+    <t>No había estudio de vida económica adjunto</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Ingresos año 1</t>
+  </si>
+  <si>
+    <t>COP 1.500 MM</t>
+  </si>
+  <si>
+    <t>Supuesto agregado del modelo</t>
+  </si>
+  <si>
+    <t>Sin catastro, consumo ni tarifa adjuntos</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>OPEX año 1</t>
+  </si>
+  <si>
+    <t>COP 1.150 MM</t>
+  </si>
+  <si>
+    <t>Supuesto agregado del modelo</t>
+  </si>
+  <si>
+    <t>Sin cotizaciones ni desglose operativo oficial</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Crecimiento nominal</t>
+  </si>
+  <si>
+    <t>3,5 % anual</t>
+  </si>
+  <si>
+    <t>Supuesto común del modelo para ingresos, OPEX y beneficios</t>
+  </si>
+  <si>
+    <t>No hay estudio macroeconómico o contractual adjunto</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Beneficio social año 1</t>
+  </si>
+  <si>
+    <t>COP 4.150 MM</t>
+  </si>
+  <si>
+    <t>Supuesto agregado del modelo</t>
+  </si>
+  <si>
+    <t>Sin estudio de salud, tiempo ni disposición a pagar</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Estructura financiera</t>
+  </si>
+  <si>
+    <t>80 % público / 10 % deuda / 10 % equity</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo</t>
+  </si>
+  <si>
+    <t>No corresponde a cierre financiero ni convenio real</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Costo aporte público</t>
+  </si>
+  <si>
+    <t>9 % nominal</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo, igualado a la tasa social adoptada</t>
+  </si>
+  <si>
+    <t>No es costo contractual observado</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Costos de capital</t>
+  </si>
+  <si>
+    <t>Kd 11 %, Ke 14 %, impuesto 35 %</t>
+  </si>
+  <si>
+    <t>Supuestos financieros del modelo</t>
+  </si>
+  <si>
+    <t>No corresponden a ofertas vinculantes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Plazo de deuda</t>
+  </si>
+  <si>
+    <t>10 años, cuota fija</t>
+  </si>
+  <si>
+    <t>Supuesto del modelo</t>
+  </si>
+  <si>
+    <t>No existe term sheet ni contrato de crédito adjunto</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Tasa social</t>
+  </si>
+  <si>
+    <t>9 %</t>
+  </si>
+  <si>
+    <t>Atribuida a metodología DNP en el caso académico</t>
+  </si>
+  <si>
+    <t>Referencia identificada pero no adjunta; confirmar vigencia</t>
+  </si>
+  <si>
+    <t>No — referencia no adjunta</t>
+  </si>
+  <si>
+    <t>Vida útil/depreciación</t>
+  </si>
+  <si>
+    <t>25 años, lineal y sin valor residual</t>
+  </si>
+  <si>
+    <t>Supuesto contable del modelo</t>
+  </si>
+  <si>
+    <t>No hay estudio de activos adjunto</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>APU y cantidades</t>
+  </si>
+  <si>
+    <t>42 actividades; AIU 25 %</t>
+  </si>
+  <si>
+    <t>Elaboración académica nueva, calibrada para conciliar COP 19.971 MM</t>
+  </si>
+  <si>
+    <t>No proviene de SECOP, diseños, APU oficiales ni cotizaciones</t>
+  </si>
+  <si>
+    <t>No — referencial</t>
+  </si>
+  <si>
+    <t>Riesgos</t>
+  </si>
+  <si>
+    <t>20 riesgos y 10 intervenciones</t>
+  </si>
+  <si>
+    <t>Análisis académico del equipo a partir del alcance</t>
+  </si>
+  <si>
+    <t>No es matriz contractual ni estudio ambiental</t>
+  </si>
+  <si>
+    <t>No — referencial</t>
+  </si>
+  <si>
+    <t>APU ACADÉMICO REFERENCIAL — COP MILLONES — NO ES APU OFICIAL NI APTO PARA CONTRATACIÓN</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Capítulo</t>
+  </si>
+  <si>
+    <t>Actividad</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Materiales/U</t>
+  </si>
+  <si>
+    <t>Mano de obra/U</t>
+  </si>
+  <si>
+    <t>Equipo/U</t>
+  </si>
+  <si>
+    <t>Transporte/U</t>
+  </si>
+  <si>
+    <t>Costo directo/U</t>
+  </si>
+  <si>
+    <t>AIU</t>
+  </si>
+  <si>
+    <t>Precio unitario</t>
+  </si>
+  <si>
+    <t>Costo parcial</t>
+  </si>
+  <si>
+    <t>Base / advertencia</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Replanteo, campamento y obras provisionales</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance preliminar referencial</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Bocatoma: excavación, concreto y protección estructural</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>Cantidad conceptual, sin planos definitivos</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Rejillas, compuertas y elementos metálicos</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Dos líneas operativas referenciales</t>
+  </si>
+  <si>
+    <t>1.04</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Desarenador y canal de entrada</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Configuración conceptual</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Tubería de aducción instalada</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Longitud y diámetro por validar</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Protección de orillas y control de erosión</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Longitud conceptual</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Pruebas, desinfección y puesta en servicio</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Actividad global referencial</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Preparación del lote, excavaciones y drenajes</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Sin levantamiento topográfico definitivo</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Estructuras hidráulicas y edificios de proceso</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Dimensionamiento conceptual 45 L/s</t>
+  </si>
+  <si>
+    <t>2.03</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Trenes de coagulación, floculación y sedimentación</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Dos trenes para flexibilidad operativa</t>
+  </si>
+  <si>
+    <t>2.04</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Filtros rápidos, medios filtrantes y accesorios</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Número referencial de filtros</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Preparación y dosificación de químicos</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Incluye almacenamiento y dosificación</t>
+  </si>
+  <si>
+    <t>2.06</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Sistema de desinfección y seguridad química</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Tecnología por definir en diseño</t>
+  </si>
+  <si>
+    <t>2.07</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Instalaciones eléctricas, control y automatización</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Instrumentación conceptual</t>
+  </si>
+  <si>
+    <t>2.08</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Laboratorio e instrumentación de calidad</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Equipamiento básico de operación</t>
+  </si>
+  <si>
+    <t>2.09</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Manejo de lodos y aguas de lavado</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Solución conceptual ambiental</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Pruebas de proceso, capacitación y arranque</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Actividad global referencial</t>
+  </si>
+  <si>
+    <t>3.01</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Tanque de almacenamiento y regulación</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>Volumen preliminar; requiere balance horario</t>
+  </si>
+  <si>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Edificio y obras civiles de estación de bombeo</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Configuración conceptual</t>
+  </si>
+  <si>
+    <t>3.03</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Bombas, motores, tableros y accesorios</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Dos operativas y una de respaldo</t>
+  </si>
+  <si>
+    <t>3.04</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Respaldo eléctrico y transferencia automática</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Potencia por definir</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Tuberías de impulsión, válvulas y control de golpe</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Diámetros y longitudes por validar</t>
+  </si>
+  <si>
+    <t>3.06</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Pruebas hidráulicas y puesta en marcha</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Actividad global referencial</t>
+  </si>
+  <si>
+    <t>4.01</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Red PVC aproximada Ø110 mm instalada</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Longitud/diámetro conceptual</t>
+  </si>
+  <si>
+    <t>4.02</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Red PVC aproximada Ø160 mm instalada</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Longitud/diámetro conceptual</t>
+  </si>
+  <si>
+    <t>4.03</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Válvulas, hidrantes y accesorios de sectorización</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Cantidad conceptual</t>
+  </si>
+  <si>
+    <t>4.04</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Conexiones domiciliarias completas</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Número de usuarios por validar</t>
+  </si>
+  <si>
+    <t>4.05</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Micromedidores instalados</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Número de usuarios por validar</t>
+  </si>
+  <si>
+    <t>4.06</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Cámaras y puntos de macromedición por sector</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Número de sectores por modelar</t>
+  </si>
+  <si>
+    <t>5.01</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Rehabilitación de redes de alcantarillado</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Longitud conceptual</t>
+  </si>
+  <si>
+    <t>5.02</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Pozos de inspección y cámaras</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Cantidad conceptual</t>
+  </si>
+  <si>
+    <t>5.03</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Colectores, descargas y obras complementarias</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance preliminar</t>
+  </si>
+  <si>
+    <t>5.04</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Estructuras especiales y cruces</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance preliminar</t>
+  </si>
+  <si>
+    <t>5.05</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Recuperación ambiental de zonas intervenidas</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Partida de cierre ajustada al presupuesto</t>
+  </si>
+  <si>
+    <t>5.06</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Pruebas, limpieza y entrega</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Actividad global referencial</t>
+  </si>
+  <si>
+    <t>6.01</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Estudios básicos y diseños de detalle</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Debe contratarse antes de obra</t>
+  </si>
+  <si>
+    <t>6.02</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Interventoría integral</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>Duración igual al horizonte de ejecución supuesto</t>
+  </si>
+  <si>
+    <t>6.03</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Gestión ambiental, permisos y seguimiento</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance académico</t>
+  </si>
+  <si>
+    <t>6.04</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Gestión social y comunicaciones</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance académico</t>
+  </si>
+  <si>
+    <t>6.05</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Gestión predial, servidumbres y legal</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Alcance académico</t>
+  </si>
+  <si>
+    <t>6.06</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Reserva técnica y ajustes de ingeniería</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>No equivale a contingencia contractual oficial</t>
+  </si>
+  <si>
+    <t>6.07</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Capacitación institucional y cierre</t>
+  </si>
+  <si>
+    <t>GLB</t>
+  </si>
+  <si>
+    <t>Fortalecimiento del operador</t>
+  </si>
+  <si>
+    <t>TOTAL APU</t>
+  </si>
+  <si>
+    <t>Debe conciliar exactamente con Presupuesto!B9</t>
+  </si>
+  <si>
+    <t>RESUMEN POR CAPÍTULO</t>
+  </si>
+  <si>
+    <t>Captación (bocatoma) y línea de aducción</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>PTAP 45 L/s (obra civil + equipos)</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Almacenamiento (tanques) y estaciones de bombeo</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Redes de distribución, conexiones y micromedición</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Optimización del alcantarillado (componente asociado)</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
+    <t>Estudios, diseños, interventoría y gestión ambiental/social</t>
+  </si>
+  <si>
+    <t>Referencial</t>
+  </si>
+  <si>
     <t>DISEÑO DE CAUDAL — RAS</t>
   </si>
   <si>
@@ -913,6 +2018,15 @@
   </si>
   <si>
     <t>&gt;1</t>
+  </si>
+  <si>
+    <t>APU vs. CAPEX</t>
+  </si>
+  <si>
+    <t>Actividades APU</t>
+  </si>
+  <si>
+    <t>Registros de trazabilidad</t>
   </si>
   <si>
     <t>Spire.XLS for Python</t>
@@ -943,11 +2057,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]-#,##0.00;–"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000;[Red]-#,##0.000000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1026,8 +2141,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7.5"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -1052,8 +2186,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1067,6 +2213,14 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FFE7E6E6"/>
       </bottom>
     </border>
   </borders>
@@ -1089,17 +2243,32 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0"/>
@@ -1146,6 +2315,66 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="4" borderId="2" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="20">
       <alignment/>
@@ -1162,6 +2391,24 @@
     <cellStyle name="Comma [0]" xfId="19"/>
     <cellStyle name="Hyperlink" xfId="20"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1249,7 +2496,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" cap="none" u="none" baseline="0">
+              <a:rPr lang="en-US" cap="none" b="1" u="none" baseline="0">
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
                 <a:cs typeface="Calibri"/>
@@ -1264,6 +2511,7 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
       </c:spPr>
     </c:title>
@@ -1302,11 +2550,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="39131915"/>
-        <c:axId val="16642916"/>
+        <c:axId val="30714406"/>
+        <c:axId val="7994199"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39131915"/>
+        <c:axId val="30714406"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1316,14 +2564,14 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="16642916"/>
+        <c:crossAx val="7994199"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16642916"/>
+        <c:axId val="7994199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1334,7 +2582,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="39131915"/>
+        <c:crossAx val="30714406"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits/>
@@ -1666,7 +2914,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.00390625" style="0" customWidth="1"/>
@@ -1675,209 +2923,1345 @@
     <col min="4" max="4" width="16.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>641</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>642</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>276</v>
+        <v>643</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B3" s="3">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>645</v>
+      </c>
+      <c r="B3" s="21">
         <f>Presupuesto!B9-SUM(Presupuesto!B3:B8)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="21">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="str">
+      <c r="D3" s="21" t="str">
         <f>IF(ABS(B3)&lt;0.01,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B4" s="3">
+    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>646</v>
+      </c>
+      <c r="B4" s="21">
         <f>SUM(Financiacion!B3:B5)-1</f>
         <v>0</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="21">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="str">
+      <c r="D4" s="21" t="str">
         <f>IF(ABS(B4)&lt;0.000001,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" s="3">
+    <row r="5" spans="1:4" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="B5" s="21">
         <f>SUM(Financiacion!C3:C5)-Presupuesto!B9</f>
         <v>0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="21">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="str">
+      <c r="D5" s="21" t="str">
         <f>IF(ABS(B5)&lt;0.01,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="B6" s="3">
+    <row r="6" spans="1:4" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="B6" s="21">
         <f>'Amortizacion Deuda'!F27</f>
         <v>2.1032064978498966E-12</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="3" t="str">
+      <c r="C6" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="D6" s="21" t="str">
         <f>IF(ABS(B6)&lt;0.01,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B7" s="3">
+    <row r="7" spans="1:4" ht="15" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>650</v>
+      </c>
+      <c r="B7" s="21">
         <f>COUNT('Flujos de Caja'!A4:A28)</f>
         <v>25</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="21">
         <f>25</f>
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="str">
+      <c r="D7" s="21" t="str">
         <f>IF(B7=25,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="3">
+    <row r="8" spans="1:4" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>651</v>
+      </c>
+      <c r="B8" s="21">
         <f>COUNT(Riesgos!A3:A22)</f>
         <v>20</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="21">
         <f>20</f>
         <v>20</v>
       </c>
-      <c r="D8" s="3" t="str">
+      <c r="D8" s="21" t="str">
         <f>IF(B8=20,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="3">
+    <row r="9" spans="1:4" ht="15" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="B9" s="21">
         <f>COUNT(Riesgos!A27:A36)</f>
         <v>10</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="21">
         <f>10</f>
         <v>10</v>
       </c>
-      <c r="D9" s="3" t="str">
+      <c r="D9" s="21" t="str">
         <f>IF(B9=10,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B10" s="3">
+    <row r="10" spans="1:4" ht="15" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="B10" s="21">
         <f>COUNTIF(Riesgos!C27:C36,"Ambiental")</f>
         <v>5</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="21">
         <f>5</f>
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="str">
+      <c r="D10" s="21" t="str">
         <f>IF(B10=5,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B11" s="3">
+    <row r="11" spans="1:4" ht="15" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="B11" s="21">
         <f>'Diseno Caudal'!B11-'Diseno Caudal'!B9</f>
         <v>3.5331680826691</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D11" s="3" t="str">
+      <c r="C11" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="D11" s="21" t="str">
         <f>IF(B11&gt;=0,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B12" s="3">
+    <row r="12" spans="1:4" ht="15" customHeight="1">
+      <c r="A12" s="21" t="s">
+        <v>656</v>
+      </c>
+      <c r="B12" s="21">
         <f>Indicadores!B10-Supuestos!B21</f>
         <v>-4.111710971699267E-13</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="3" t="str">
+      <c r="C12" s="21" t="s">
+        <v>657</v>
+      </c>
+      <c r="D12" s="21" t="str">
         <f>IF(ABS(B12)&lt;0.000001,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="3">
+    <row r="13" spans="1:4" ht="15" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>658</v>
+      </c>
+      <c r="B13" s="21">
         <f>Indicadores!B9</f>
         <v>1.5583457184604053</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D13" s="3" t="str">
+      <c r="C13" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="D13" s="21" t="str">
         <f>IF(B13&gt;1,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
     </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1">
+      <c r="A14" s="21" t="s">
+        <v>660</v>
+      </c>
+      <c r="B14" s="21">
+        <f>'APU Referencial'!M46-Presupuesto!B9</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="21">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="21" t="str">
+        <f>IF(ABS(B14)&lt;0.01,"OK","REVISAR")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="B15" s="21">
+        <f>COUNTA('APU Referencial'!A3:A44)</f>
+        <v>42</v>
+      </c>
+      <c r="C15" s="21">
+        <f>42</f>
+        <v>42</v>
+      </c>
+      <c r="D15" s="21" t="str">
+        <f>IF(B15=42,"OK","REVISAR")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="B16" s="21">
+        <f>COUNTA(Fuentes!A3:A26)</f>
+        <v>24</v>
+      </c>
+      <c r="C16" s="21">
+        <f>24</f>
+        <v>24</v>
+      </c>
+      <c r="D16" s="21" t="str">
+        <f>IF(B16=24,"OK","REVISAR")</f>
+        <v>OK</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D14:D16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>D14="OK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>D14="REVISAR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AF8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="32" width="13.00390625" style="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="33">
+        <v>0</v>
+      </c>
+      <c r="H2" s="33">
+        <v>1</v>
+      </c>
+      <c r="I2" s="33">
+        <v>2</v>
+      </c>
+      <c r="J2" s="33">
+        <v>3</v>
+      </c>
+      <c r="K2" s="33">
+        <v>4</v>
+      </c>
+      <c r="L2" s="33">
+        <v>5</v>
+      </c>
+      <c r="M2" s="33">
+        <v>6</v>
+      </c>
+      <c r="N2" s="33">
+        <v>7</v>
+      </c>
+      <c r="O2" s="33">
+        <v>8</v>
+      </c>
+      <c r="P2" s="33">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="33">
+        <v>10</v>
+      </c>
+      <c r="R2" s="33">
+        <v>11</v>
+      </c>
+      <c r="S2" s="33">
+        <v>12</v>
+      </c>
+      <c r="T2" s="33">
+        <v>13</v>
+      </c>
+      <c r="U2" s="33">
+        <v>14</v>
+      </c>
+      <c r="V2" s="33">
+        <v>15</v>
+      </c>
+      <c r="W2" s="33">
+        <v>16</v>
+      </c>
+      <c r="X2" s="33">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="33">
+        <v>18</v>
+      </c>
+      <c r="Z2" s="33">
+        <v>19</v>
+      </c>
+      <c r="AA2" s="33">
+        <v>20</v>
+      </c>
+      <c r="AB2" s="33">
+        <v>21</v>
+      </c>
+      <c r="AC2" s="33">
+        <v>22</v>
+      </c>
+      <c r="AD2" s="33">
+        <v>23</v>
+      </c>
+      <c r="AE2" s="33">
+        <v>24</v>
+      </c>
+      <c r="AF2" s="33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="15" customHeight="1">
+      <c r="A3" s="13">
+        <v>0</v>
+      </c>
+      <c r="B3" s="14">
+        <f>(1-A3)/2*Presupuesto!$B$9</f>
+        <v>9985.5</v>
+      </c>
+      <c r="C3" s="14">
+        <f>(1-A3)/2*Presupuesto!$B$9</f>
+        <v>9985.5</v>
+      </c>
+      <c r="D3" s="15">
+        <f>IRR(G3:AF3)</f>
+        <v>-0.05397940689416905</v>
+      </c>
+      <c r="E3" s="14">
+        <f>NPV(Supuestos!$B$22,H3:AF3)+G3</f>
+        <v>-15794.058409020663</v>
+      </c>
+      <c r="F3" s="14" t="str">
+        <f>IF(D3&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+      <c r="G3" s="14">
+        <f>-C3</f>
+        <v>-9985.5</v>
+      </c>
+      <c r="H3" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1345.5521502819893</v>
+      </c>
+      <c r="I3" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1333.3021502819888</v>
+      </c>
+      <c r="J3" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1320.6234002819888</v>
+      </c>
+      <c r="K3" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1307.500894031989</v>
+      </c>
+      <c r="L3" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1293.919100063239</v>
+      </c>
+      <c r="M3" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1279.8619433055892</v>
+      </c>
+      <c r="N3" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1265.3127860614088</v>
+      </c>
+      <c r="O3" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1250.2544083136877</v>
+      </c>
+      <c r="P3" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1234.6689873447986</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-1218.538076642001</v>
+      </c>
+      <c r="R3" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S3" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T3" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U3" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V3" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W3" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X3" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y3" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z3" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA3" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB3" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC3" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD3" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE3" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF3" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15" customHeight="1">
+      <c r="A4" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="B4" s="14">
+        <f>(1-A4)/2*Presupuesto!$B$9</f>
+        <v>5991.3</v>
+      </c>
+      <c r="C4" s="14">
+        <f>(1-A4)/2*Presupuesto!$B$9</f>
+        <v>5991.3</v>
+      </c>
+      <c r="D4" s="15">
+        <f>IRR(G4:AF4)</f>
+        <v>-0.014606345852164413</v>
+      </c>
+      <c r="E4" s="14">
+        <f>NPV(Supuestos!$B$22,H4:AF4)+G4</f>
+        <v>-8262.179968943623</v>
+      </c>
+      <c r="F4" s="14" t="str">
+        <f>IF(D4&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+      <c r="G4" s="14">
+        <f>-C4</f>
+        <v>-5991.3</v>
+      </c>
+      <c r="H4" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-667.3312901691934</v>
+      </c>
+      <c r="I4" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-655.0812901691934</v>
+      </c>
+      <c r="J4" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-642.4025401691933</v>
+      </c>
+      <c r="K4" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-629.2800339191958</v>
+      </c>
+      <c r="L4" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-615.6982399504434</v>
+      </c>
+      <c r="M4" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-601.6410831927935</v>
+      </c>
+      <c r="N4" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-587.0919259486129</v>
+      </c>
+      <c r="O4" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-572.0335482008929</v>
+      </c>
+      <c r="P4" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-556.4481272320008</v>
+      </c>
+      <c r="Q4" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-540.3172165292027</v>
+      </c>
+      <c r="R4" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S4" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T4" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U4" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V4" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W4" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X4" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y4" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z4" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA4" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB4" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC4" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD4" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE4" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF4" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="15" customHeight="1">
+      <c r="A5" s="13">
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="14">
+        <f>(1-A5)/2*Presupuesto!$B$9</f>
+        <v>3994.2</v>
+      </c>
+      <c r="C5" s="14">
+        <f>(1-A5)/2*Presupuesto!$B$9</f>
+        <v>3994.2</v>
+      </c>
+      <c r="D5" s="15">
+        <f>IRR(G5:AF5)</f>
+        <v>0.021826211162366136</v>
+      </c>
+      <c r="E5" s="14">
+        <f>NPV(Supuestos!$B$22,H5:AF5)+G5</f>
+        <v>-4496.240748905102</v>
+      </c>
+      <c r="F5" s="14" t="str">
+        <f>IF(D5&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+      <c r="G5" s="14">
+        <f>-C5</f>
+        <v>-3994.2</v>
+      </c>
+      <c r="H5" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-328.22086011279555</v>
+      </c>
+      <c r="I5" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-315.9708601127956</v>
+      </c>
+      <c r="J5" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-303.292110112796</v>
+      </c>
+      <c r="K5" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-290.1696038627955</v>
+      </c>
+      <c r="L5" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-276.58780989404556</v>
+      </c>
+      <c r="M5" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-262.53065313639576</v>
+      </c>
+      <c r="N5" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-247.98149589221558</v>
+      </c>
+      <c r="O5" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-232.92311814449505</v>
+      </c>
+      <c r="P5" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-217.33769717560762</v>
+      </c>
+      <c r="Q5" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-201.2067864728034</v>
+      </c>
+      <c r="R5" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S5" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T5" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U5" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V5" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W5" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X5" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y5" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z5" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA5" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB5" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC5" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD5" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE5" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF5" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="15" customHeight="1">
+      <c r="A6" s="13">
+        <v>0.7</v>
+      </c>
+      <c r="B6" s="14">
+        <f>(1-A6)/2*Presupuesto!$B$9</f>
+        <v>2995.65</v>
+      </c>
+      <c r="C6" s="14">
+        <f>(1-A6)/2*Presupuesto!$B$9</f>
+        <v>2995.65</v>
+      </c>
+      <c r="D6" s="15">
+        <f>IRR(G6:AF6)</f>
+        <v>0.05203632439827555</v>
+      </c>
+      <c r="E6" s="14">
+        <f>NPV(Supuestos!$B$22,H6:AF6)+G6</f>
+        <v>-2613.271138885842</v>
+      </c>
+      <c r="F6" s="14" t="str">
+        <f>IF(D6&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+      <c r="G6" s="14">
+        <f>-C6</f>
+        <v>-2995.65</v>
+      </c>
+      <c r="H6" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-158.66564508459672</v>
+      </c>
+      <c r="I6" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-146.41564508459666</v>
+      </c>
+      <c r="J6" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-133.73689508459665</v>
+      </c>
+      <c r="K6" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-120.61438883459664</v>
+      </c>
+      <c r="L6" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-107.0325948658467</v>
+      </c>
+      <c r="M6" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-92.97543810819684</v>
+      </c>
+      <c r="N6" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-78.42628086401669</v>
+      </c>
+      <c r="O6" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-63.36790311629716</v>
+      </c>
+      <c r="P6" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-47.782482147406654</v>
+      </c>
+      <c r="Q6" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>-31.65157144460659</v>
+      </c>
+      <c r="R6" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S6" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T6" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U6" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V6" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W6" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X6" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y6" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z6" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA6" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB6" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC6" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD6" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE6" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF6" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" ht="15" customHeight="1">
+      <c r="A7" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="14">
+        <f>(1-A7)/2*Presupuesto!$B$9</f>
+        <v>1997.1</v>
+      </c>
+      <c r="C7" s="14">
+        <f>(1-A7)/2*Presupuesto!$B$9</f>
+        <v>1997.1</v>
+      </c>
+      <c r="D7" s="15">
+        <f>IRR(G7:AF7)</f>
+        <v>0.1046108925530724</v>
+      </c>
+      <c r="E7" s="14">
+        <f>NPV(Supuestos!$B$22,H7:AF7)+G7</f>
+        <v>-730.3015288665811</v>
+      </c>
+      <c r="F7" s="14" t="str">
+        <f>IF(D7&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+      <c r="G7" s="14">
+        <f>-C7</f>
+        <v>-1997.1</v>
+      </c>
+      <c r="H7" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>10.889569943602211</v>
+      </c>
+      <c r="I7" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>23.139569943602197</v>
+      </c>
+      <c r="J7" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>35.81831994360223</v>
+      </c>
+      <c r="K7" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>48.94082619360228</v>
+      </c>
+      <c r="L7" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>62.52262016235218</v>
+      </c>
+      <c r="M7" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>76.57977692000202</v>
+      </c>
+      <c r="N7" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>91.12893416418223</v>
+      </c>
+      <c r="O7" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>106.18731191190221</v>
+      </c>
+      <c r="P7" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>121.77273288079226</v>
+      </c>
+      <c r="Q7" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>137.90364358359233</v>
+      </c>
+      <c r="R7" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S7" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T7" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U7" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V7" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W7" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X7" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y7" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z7" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA7" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB7" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC7" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD7" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE7" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF7" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="15" customHeight="1">
+      <c r="A8" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="B8" s="14">
+        <f>(1-A8)/2*Presupuesto!$B$9</f>
+        <v>998.55</v>
+      </c>
+      <c r="C8" s="14">
+        <f>(1-A8)/2*Presupuesto!$B$9</f>
+        <v>998.55</v>
+      </c>
+      <c r="D8" s="15">
+        <f>IRR(G8:AF8)</f>
+        <v>0.2517685608889223</v>
+      </c>
+      <c r="E8" s="14">
+        <f>NPV(Supuestos!$B$22,H8:AF8)+G8</f>
+        <v>1152.6680811526796</v>
+      </c>
+      <c r="F8" s="14" t="str">
+        <f>IF(D8&gt;=Supuestos!$B$22,"Viable","No viable")</f>
+        <v>Viable</v>
+      </c>
+      <c r="G8" s="14">
+        <f>-C8</f>
+        <v>-998.55</v>
+      </c>
+      <c r="H8" s="14">
+        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>180.44478497180108</v>
+      </c>
+      <c r="I8" s="14">
+        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>192.6947849718011</v>
+      </c>
+      <c r="J8" s="14">
+        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>205.37353497180118</v>
+      </c>
+      <c r="K8" s="14">
+        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>218.4960412218012</v>
+      </c>
+      <c r="L8" s="14">
+        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>232.07783519055107</v>
+      </c>
+      <c r="M8" s="14">
+        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>246.13499194820096</v>
+      </c>
+      <c r="N8" s="14">
+        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>260.6841491923811</v>
+      </c>
+      <c r="O8" s="14">
+        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>275.7425269401012</v>
+      </c>
+      <c r="P8" s="14">
+        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>291.32794790899123</v>
+      </c>
+      <c r="Q8" s="14">
+        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>307.458858611791</v>
+      </c>
+      <c r="R8" s="14">
+        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>493.7095662173897</v>
+      </c>
+      <c r="S8" s="14">
+        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>510.9894010349999</v>
+      </c>
+      <c r="T8" s="14">
+        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>528.87403007123</v>
+      </c>
+      <c r="U8" s="14">
+        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>547.3846211237101</v>
+      </c>
+      <c r="V8" s="14">
+        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>566.5430828630499</v>
+      </c>
+      <c r="W8" s="14">
+        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>586.3720907632598</v>
+      </c>
+      <c r="X8" s="14">
+        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>606.8951139399701</v>
+      </c>
+      <c r="Y8" s="14">
+        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>628.1364429278701</v>
+      </c>
+      <c r="Z8" s="14">
+        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>650.1212184303399</v>
+      </c>
+      <c r="AA8" s="14">
+        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>672.8754610753999</v>
+      </c>
+      <c r="AB8" s="14">
+        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>696.4261022130399</v>
+      </c>
+      <c r="AC8" s="14">
+        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>720.8010157904996</v>
+      </c>
+      <c r="AD8" s="14">
+        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>746.0290513431701</v>
+      </c>
+      <c r="AE8" s="14">
+        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>772.1400681401801</v>
+      </c>
+      <c r="AF8" s="14">
+        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
+        <v>799.0512308413083</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:AF2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AF1"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.00390625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="20.00390625" style="0" customWidth="1"/>
+    <col min="3" max="3" width="24.00390625" style="0" customWidth="1"/>
+    <col min="4" max="4" width="27.00390625" style="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="10">
+        <f>Financiacion!B8</f>
+        <v>0.09315</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="8">
+        <f>NPV(B3,'Flujos de Caja'!L4:L28)+'Flujos de Caja'!L3</f>
+        <v>-15486.829598504228</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="21" t="str">
+        <f>IF(B4&gt;0,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="10">
+        <f>IRR('Flujos de Caja'!L3:L28)</f>
+        <v>-0.024525933826823654</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="21" t="str">
+        <f>IF(B5&gt;B3,"Viable","No viable")</f>
+        <v>No viable</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="8">
+        <f>NPV(Supuestos!B22,'Flujos de Caja'!M4:M28)+'Flujos de Caja'!M3</f>
+        <v>-730.3015288665811</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="21" t="str">
+        <f>IF(B6&gt;0,"Viable","No alcanza Ke")</f>
+        <v>No alcanza Ke</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="10">
+        <f>IRR('Flujos de Caja'!M3:M28)</f>
+        <v>0.10461089255307242</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="21" t="str">
+        <f>IF(B7&gt;Supuestos!B22,"Viable","No alcanza Ke")</f>
+        <v>No alcanza Ke</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="8">
+        <f>NPV(Supuestos!B25,'Flujos de Caja'!P4:P28)+'Flujos de Caja'!P3</f>
+        <v>19625.705143047235</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="21" t="str">
+        <f>IF(B8&gt;0,"Viable","No viable")</f>
+        <v>Viable</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="21">
+        <f>NPV(Supuestos!B25,'Flujos de Caja'!O4:O28)/(Presupuesto!B9+NPV(Supuestos!B25,'Flujos de Caja'!C4:C28))</f>
+        <v>1.5583457184604053</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="21" t="str">
+        <f>IF(B9&gt;1,"Viable","No viable")</f>
+        <v>Viable</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="10">
+        <f>IRR('Flujos de Caja'!N3:N28)</f>
+        <v>0.10999999999958883</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="21" t="str">
+        <f>IF(ABS(B10-Supuestos!B21)&lt;0.000001,"Concilia","Revisar")</f>
+        <v>Concilia</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -1890,7 +4274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1907,38 +4291,38 @@
     <col min="8" max="8" width="16.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:8" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -1966,7 +4350,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15">
+    <row r="4" spans="1:8" ht="15" customHeight="1">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -1992,7 +4376,7 @@
       </c>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:8" ht="15" customHeight="1">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -2018,7 +4402,7 @@
       </c>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:8" ht="15">
+    <row r="6" spans="1:8" ht="15" customHeight="1">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -2046,7 +4430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:8" ht="15" customHeight="1">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -2072,7 +4456,7 @@
       </c>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -2100,7 +4484,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15">
+    <row r="9" spans="1:8" ht="15" customHeight="1">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -2126,7 +4510,7 @@
       </c>
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:8" ht="15">
+    <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -2154,7 +4538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15">
+    <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -2182,7 +4566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15">
+    <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -2208,7 +4592,7 @@
       </c>
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:8" ht="15">
+    <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -2234,7 +4618,7 @@
       </c>
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:8" ht="15">
+    <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -2260,7 +4644,7 @@
       </c>
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:8" ht="15">
+    <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -2286,7 +4670,7 @@
       </c>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:8" ht="15">
+    <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -2312,7 +4696,7 @@
       </c>
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="1:8" ht="15">
+    <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="11">
         <v>15</v>
       </c>
@@ -2338,7 +4722,7 @@
       </c>
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="1:8" ht="15">
+    <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="11">
         <v>16</v>
       </c>
@@ -2364,7 +4748,7 @@
       </c>
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="1:8" ht="15">
+    <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="11">
         <v>17</v>
       </c>
@@ -2390,7 +4774,7 @@
       </c>
       <c r="H19" s="11"/>
     </row>
-    <row r="20" spans="1:8" ht="15">
+    <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="11">
         <v>18</v>
       </c>
@@ -2416,7 +4800,7 @@
       </c>
       <c r="H20" s="11"/>
     </row>
-    <row r="21" spans="1:8" ht="15">
+    <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="11">
         <v>19</v>
       </c>
@@ -2442,7 +4826,7 @@
       </c>
       <c r="H21" s="11"/>
     </row>
-    <row r="22" spans="1:8" ht="15">
+    <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="11">
         <v>20</v>
       </c>
@@ -2473,13 +4857,13 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" ht="15"/>
-    <row r="25" ht="15">
-      <c r="A25" s="16" t="s">
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="30" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15">
+    <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>56</v>
       </c>
@@ -2505,7 +4889,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15">
+    <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="11">
         <v>1</v>
       </c>
@@ -2533,7 +4917,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15">
+    <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="11">
         <v>6</v>
       </c>
@@ -2561,7 +4945,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15">
+    <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="11">
         <v>4</v>
       </c>
@@ -2589,7 +4973,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="15">
+    <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="11">
         <v>8</v>
       </c>
@@ -2617,7 +5001,7 @@
         <v>Medio</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15">
+    <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="11">
         <v>9</v>
       </c>
@@ -2645,7 +5029,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15">
+    <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="11">
         <v>10</v>
       </c>
@@ -2673,7 +5057,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15">
+    <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="11">
         <v>11</v>
       </c>
@@ -2701,7 +5085,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15">
+    <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="11">
         <v>12</v>
       </c>
@@ -2729,7 +5113,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15">
+    <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="11">
         <v>16</v>
       </c>
@@ -2757,7 +5141,7 @@
         <v>Bajo</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15">
+    <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="11">
         <v>15</v>
       </c>
@@ -2814,359 +5198,359 @@
     <col min="4" max="4" width="55.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>565</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>568</v>
       </c>
       <c r="B3" s="6">
         <v>17000</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>204</v>
+      <c r="C3" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>571</v>
       </c>
       <c r="B4" s="6">
         <v>10957</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>207</v>
+      <c r="C4" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>574</v>
       </c>
       <c r="B5" s="7">
         <v>0.012</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>210</v>
+      <c r="C5" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>577</v>
       </c>
       <c r="B6" s="6">
         <v>25</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="3" t="s">
-        <v>213</v>
+      <c r="C6" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>580</v>
       </c>
       <c r="B7" s="6">
         <v>140</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>216</v>
+      <c r="C7" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>583</v>
       </c>
       <c r="B8" s="7">
         <v>0.25</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="3" t="s">
-        <v>219</v>
+      <c r="C8" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>586</v>
       </c>
       <c r="B9" s="6">
         <v>1.3</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="3" t="s">
-        <v>222</v>
+      <c r="C9" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>589</v>
       </c>
       <c r="B10" s="6">
         <v>1.6</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15">
-      <c r="A11" s="3" t="s">
-        <v>225</v>
+      <c r="C10" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>592</v>
       </c>
       <c r="B11" s="6">
         <v>45</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="3" t="s">
-        <v>228</v>
+      <c r="C11" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1">
+      <c r="A12" s="21" t="s">
+        <v>595</v>
       </c>
       <c r="B12" s="6">
         <v>25</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="3" t="s">
-        <v>231</v>
+      <c r="C12" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1">
+      <c r="A13" s="21" t="s">
+        <v>598</v>
       </c>
       <c r="B13" s="6">
         <v>1500</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="3" t="s">
-        <v>234</v>
+      <c r="C13" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1">
+      <c r="A14" s="21" t="s">
+        <v>601</v>
       </c>
       <c r="B14" s="6">
         <v>1150</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15">
-      <c r="A15" s="3" t="s">
-        <v>237</v>
+      <c r="C14" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>604</v>
       </c>
       <c r="B15" s="7">
         <v>0.035</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="3" t="s">
-        <v>240</v>
+      <c r="C15" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>607</v>
       </c>
       <c r="B16" s="6">
         <v>4150</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="3" t="s">
-        <v>243</v>
+      <c r="C16" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1">
+      <c r="A17" s="21" t="s">
+        <v>610</v>
       </c>
       <c r="B17" s="7">
         <v>0.8</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="A18" s="3" t="s">
-        <v>246</v>
+      <c r="C17" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1">
+      <c r="A18" s="21" t="s">
+        <v>613</v>
       </c>
       <c r="B18" s="7">
         <v>0.1</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15">
-      <c r="A19" s="3" t="s">
-        <v>249</v>
+      <c r="C18" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1">
+      <c r="A19" s="21" t="s">
+        <v>616</v>
       </c>
       <c r="B19" s="7">
         <v>0.1</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" s="3" t="s">
-        <v>252</v>
+      <c r="C19" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>619</v>
       </c>
       <c r="B20" s="7">
         <v>0.09</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15">
-      <c r="A21" s="3" t="s">
-        <v>255</v>
+      <c r="C20" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>622</v>
       </c>
       <c r="B21" s="7">
         <v>0.11</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15">
-      <c r="A22" s="3" t="s">
-        <v>258</v>
+      <c r="C21" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>625</v>
       </c>
       <c r="B22" s="7">
         <v>0.14</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15">
-      <c r="A23" s="3" t="s">
-        <v>261</v>
+      <c r="C22" s="21" t="s">
+        <v>626</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>628</v>
       </c>
       <c r="B23" s="7">
         <v>0.35</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15">
-      <c r="A24" s="3" t="s">
-        <v>264</v>
+      <c r="C23" s="21" t="s">
+        <v>629</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>631</v>
       </c>
       <c r="B24" s="6">
         <v>10</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15">
-      <c r="A25" s="3" t="s">
-        <v>267</v>
+      <c r="C24" s="21" t="s">
+        <v>632</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>634</v>
       </c>
       <c r="B25" s="7">
         <v>0.09</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="3" t="s">
-        <v>270</v>
+      <c r="C25" s="21" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15" customHeight="1">
+      <c r="A26" s="21" t="s">
+        <v>637</v>
       </c>
       <c r="B26" s="6">
         <v>25</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>272</v>
+      <c r="C26" s="21" t="s">
+        <v>638</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -3196,128 +5580,128 @@
     <col min="3" max="3" width="40.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>178</v>
+        <v>541</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>542</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>545</v>
       </c>
       <c r="B3" s="8">
         <f>Supuestos!B3</f>
         <v>17000</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>180</v>
+      <c r="C3" s="21" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>547</v>
       </c>
       <c r="B4" s="8">
         <f>Supuestos!B4</f>
         <v>10957</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>182</v>
+      <c r="C4" s="21" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>549</v>
       </c>
       <c r="B5" s="8">
         <f>B4*(1+Supuestos!$B$5)^Supuestos!$B$6</f>
         <v>14764.0148804563</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>184</v>
+      <c r="C5" s="21" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>551</v>
       </c>
       <c r="B6" s="8">
         <f>Supuestos!B7</f>
         <v>140</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="3" t="s">
-        <v>186</v>
+      <c r="C6" s="21" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>553</v>
       </c>
       <c r="B7" s="8">
         <f>B6/(1-Supuestos!$B$8)</f>
         <v>186.66666666666666</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
+      <c r="C7" s="21" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>555</v>
       </c>
       <c r="B8" s="8">
         <f>B5*B7/86400</f>
         <v>31.897563013331478</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15">
-      <c r="A9" s="3" t="s">
-        <v>190</v>
+      <c r="C8" s="21" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>557</v>
       </c>
       <c r="B9" s="8">
         <f>B8*Supuestos!$B$9</f>
         <v>41.4668319173309</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15">
-      <c r="A10" s="3" t="s">
-        <v>192</v>
+      <c r="C9" s="21" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1">
+      <c r="A10" s="21" t="s">
+        <v>559</v>
       </c>
       <c r="B10" s="8">
         <f>B9*Supuestos!$B$10</f>
         <v>66.3469310677294</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15">
-      <c r="A11" s="3" t="s">
-        <v>194</v>
+      <c r="C10" s="21" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1">
+      <c r="A11" s="21" t="s">
+        <v>561</v>
       </c>
       <c r="B11" s="8">
         <f>Supuestos!B11</f>
         <v>45</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>195</v>
+      <c r="C11" s="21" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -3339,125 +5723,2182 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="62.00390625" style="0" customWidth="1"/>
-    <col min="2" max="2" width="18.00390625" style="0" customWidth="1"/>
-    <col min="3" max="3" width="15.00390625" style="0" customWidth="1"/>
+    <col min="1" max="1" width="10.00390625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="43.00390625" style="0" customWidth="1"/>
+    <col min="3" max="3" width="48.00390625" style="0" customWidth="1"/>
+    <col min="4" max="4" width="10.00390625" style="0" customWidth="1"/>
+    <col min="5" max="5" width="12.00390625" style="0" customWidth="1"/>
+    <col min="6" max="7" width="15.00390625" style="0" customWidth="1"/>
+    <col min="8" max="8" width="13.00390625" style="0" customWidth="1"/>
+    <col min="9" max="9" width="15.00390625" style="0" customWidth="1"/>
+    <col min="10" max="10" width="16.00390625" style="0" customWidth="1"/>
+    <col min="11" max="11" width="10.00390625" style="0" customWidth="1"/>
+    <col min="12" max="12" width="16.00390625" style="0" customWidth="1"/>
+    <col min="13" max="13" width="17.00390625" style="0" customWidth="1"/>
+    <col min="14" max="14" width="45.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="6">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1">
+      <c r="A2" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15" customHeight="1">
+      <c r="A3" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="25">
+        <v>1</v>
+      </c>
+      <c r="F3" s="25">
+        <v>64.8</v>
+      </c>
+      <c r="G3" s="25">
+        <v>36</v>
+      </c>
+      <c r="H3" s="25">
+        <v>28.8</v>
+      </c>
+      <c r="I3" s="25">
+        <v>14.4</v>
+      </c>
+      <c r="J3" s="26">
+        <f>SUM(F3:I3)</f>
+        <v>144</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L3" s="26">
+        <f>J3*(1+K3)</f>
+        <v>180</v>
+      </c>
+      <c r="M3" s="26">
+        <f>E3*L3</f>
+        <v>180</v>
+      </c>
+      <c r="N3" s="24" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1">
+      <c r="A4" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="E4" s="25">
+        <v>300</v>
+      </c>
+      <c r="F4" s="25">
+        <v>1.08</v>
+      </c>
+      <c r="G4" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="H4" s="25">
+        <v>0.48</v>
+      </c>
+      <c r="I4" s="25">
+        <v>0.24</v>
+      </c>
+      <c r="J4" s="26">
+        <f>SUM(F4:I4)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="K4" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L4" s="26">
+        <f>J4*(1+K4)</f>
+        <v>3</v>
+      </c>
+      <c r="M4" s="26">
+        <f>E4*L4</f>
+        <v>900</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1">
+      <c r="A5" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E5" s="25">
+        <v>2</v>
+      </c>
+      <c r="F5" s="25">
+        <v>62.4</v>
+      </c>
+      <c r="G5" s="25">
+        <v>14.4</v>
+      </c>
+      <c r="H5" s="25">
+        <v>14.4</v>
+      </c>
+      <c r="I5" s="25">
+        <v>4.8</v>
+      </c>
+      <c r="J5" s="26">
+        <f>SUM(F5:I5)</f>
+        <v>96</v>
+      </c>
+      <c r="K5" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L5" s="26">
+        <f>J5*(1+K5)</f>
+        <v>120</v>
+      </c>
+      <c r="M5" s="26">
+        <f>E5*L5</f>
+        <v>240</v>
+      </c>
+      <c r="N5" s="24" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1">
+      <c r="A6" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="E6" s="25">
+        <v>1</v>
+      </c>
+      <c r="F6" s="25">
+        <v>126</v>
+      </c>
+      <c r="G6" s="25">
+        <v>70</v>
+      </c>
+      <c r="H6" s="25">
+        <v>56</v>
+      </c>
+      <c r="I6" s="25">
+        <v>28</v>
+      </c>
+      <c r="J6" s="26">
+        <f>SUM(F6:I6)</f>
+        <v>280</v>
+      </c>
+      <c r="K6" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L6" s="26">
+        <f>J6*(1+K6)</f>
+        <v>350</v>
+      </c>
+      <c r="M6" s="26">
+        <f>E6*L6</f>
+        <v>350</v>
+      </c>
+      <c r="N6" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1">
+      <c r="A7" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="E7" s="25">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="25">
+        <v>0.0792</v>
+      </c>
+      <c r="G7" s="25">
+        <v>0.0288</v>
+      </c>
+      <c r="H7" s="25">
+        <v>0.0216</v>
+      </c>
+      <c r="I7" s="25">
+        <v>0.0144</v>
+      </c>
+      <c r="J7" s="26">
+        <f>SUM(F7:I7)</f>
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="K7" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L7" s="26">
+        <f>J7*(1+K7)</f>
+        <v>0.18</v>
+      </c>
+      <c r="M7" s="26">
+        <f>E7*L7</f>
+        <v>540</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1">
+      <c r="A8" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="E8" s="25">
+        <v>500</v>
+      </c>
+      <c r="F8" s="25">
+        <v>0.0864</v>
+      </c>
+      <c r="G8" s="25">
+        <v>0.048</v>
+      </c>
+      <c r="H8" s="25">
+        <v>0.0384</v>
+      </c>
+      <c r="I8" s="25">
+        <v>0.0192</v>
+      </c>
+      <c r="J8" s="26">
+        <f>SUM(F8:I8)</f>
+        <v>0.192</v>
+      </c>
+      <c r="K8" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L8" s="26">
+        <f>J8*(1+K8)</f>
+        <v>0.24</v>
+      </c>
+      <c r="M8" s="26">
+        <f>E8*L8</f>
+        <v>120</v>
+      </c>
+      <c r="N8" s="24" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1">
+      <c r="A9" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="25">
+        <v>1</v>
+      </c>
+      <c r="F9" s="25">
+        <v>8.4</v>
+      </c>
+      <c r="G9" s="25">
+        <v>30.8</v>
+      </c>
+      <c r="H9" s="25">
+        <v>11.2</v>
+      </c>
+      <c r="I9" s="25">
+        <v>5.6</v>
+      </c>
+      <c r="J9" s="26">
+        <f>SUM(F9:I9)</f>
+        <v>56.00000000000001</v>
+      </c>
+      <c r="K9" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="26">
+        <f>J9*(1+K9)</f>
+        <v>70</v>
+      </c>
+      <c r="M9" s="26">
+        <f>E9*L9</f>
+        <v>70</v>
+      </c>
+      <c r="N9" s="24" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1">
+      <c r="A10" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="E10" s="25">
+        <v>1</v>
+      </c>
+      <c r="F10" s="25">
+        <v>126</v>
+      </c>
+      <c r="G10" s="25">
+        <v>70</v>
+      </c>
+      <c r="H10" s="25">
+        <v>56</v>
+      </c>
+      <c r="I10" s="25">
+        <v>28</v>
+      </c>
+      <c r="J10" s="26">
+        <f>SUM(F10:I10)</f>
+        <v>280</v>
+      </c>
+      <c r="K10" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L10" s="26">
+        <f>J10*(1+K10)</f>
+        <v>350</v>
+      </c>
+      <c r="M10" s="26">
+        <f>E10*L10</f>
+        <v>350</v>
+      </c>
+      <c r="N10" s="24" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1">
+      <c r="A11" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="E11" s="25">
+        <v>1</v>
+      </c>
+      <c r="F11" s="25">
+        <v>504</v>
+      </c>
+      <c r="G11" s="25">
+        <v>280</v>
+      </c>
+      <c r="H11" s="25">
+        <v>224</v>
+      </c>
+      <c r="I11" s="25">
+        <v>112</v>
+      </c>
+      <c r="J11" s="26">
+        <f>SUM(F11:I11)</f>
+        <v>1120</v>
+      </c>
+      <c r="K11" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L11" s="26">
+        <f>J11*(1+K11)</f>
+        <v>1400</v>
+      </c>
+      <c r="M11" s="26">
+        <f>E11*L11</f>
+        <v>1400</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1">
+      <c r="A12" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>362</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E12" s="25">
+        <v>2</v>
+      </c>
+      <c r="F12" s="25">
+        <v>286</v>
+      </c>
+      <c r="G12" s="25">
+        <v>66</v>
+      </c>
+      <c r="H12" s="25">
+        <v>66</v>
+      </c>
+      <c r="I12" s="25">
+        <v>22</v>
+      </c>
+      <c r="J12" s="26">
+        <f>SUM(F12:I12)</f>
+        <v>440</v>
+      </c>
+      <c r="K12" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L12" s="26">
+        <f>J12*(1+K12)</f>
+        <v>550</v>
+      </c>
+      <c r="M12" s="26">
+        <f>E12*L12</f>
+        <v>1100</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1">
+      <c r="A13" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="E13" s="25">
+        <v>4</v>
+      </c>
+      <c r="F13" s="25">
+        <v>110.5</v>
+      </c>
+      <c r="G13" s="25">
+        <v>25.5</v>
+      </c>
+      <c r="H13" s="25">
+        <v>25.5</v>
+      </c>
+      <c r="I13" s="25">
+        <v>8.5</v>
+      </c>
+      <c r="J13" s="26">
+        <f>SUM(F13:I13)</f>
+        <v>170</v>
+      </c>
+      <c r="K13" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L13" s="26">
+        <f>J13*(1+K13)</f>
+        <v>212.5</v>
+      </c>
+      <c r="M13" s="26">
+        <f>E13*L13</f>
+        <v>850</v>
+      </c>
+      <c r="N13" s="24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="A14" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="E14" s="25">
+        <v>1</v>
+      </c>
+      <c r="F14" s="25">
+        <v>338</v>
+      </c>
+      <c r="G14" s="25">
+        <v>78</v>
+      </c>
+      <c r="H14" s="25">
+        <v>78</v>
+      </c>
+      <c r="I14" s="25">
+        <v>26</v>
+      </c>
+      <c r="J14" s="26">
+        <f>SUM(F14:I14)</f>
+        <v>520</v>
+      </c>
+      <c r="K14" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L14" s="26">
+        <f>J14*(1+K14)</f>
+        <v>650</v>
+      </c>
+      <c r="M14" s="26">
+        <f>E14*L14</f>
+        <v>650</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15" customHeight="1">
+      <c r="A15" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="E15" s="25">
+        <v>1</v>
+      </c>
+      <c r="F15" s="25">
+        <v>156</v>
+      </c>
+      <c r="G15" s="25">
+        <v>36</v>
+      </c>
+      <c r="H15" s="25">
+        <v>36</v>
+      </c>
+      <c r="I15" s="25">
+        <v>12</v>
+      </c>
+      <c r="J15" s="26">
+        <f>SUM(F15:I15)</f>
+        <v>240</v>
+      </c>
+      <c r="K15" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L15" s="26">
+        <f>J15*(1+K15)</f>
+        <v>300</v>
+      </c>
+      <c r="M15" s="26">
+        <f>E15*L15</f>
+        <v>300</v>
+      </c>
+      <c r="N15" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1">
+      <c r="A16" s="24" t="s">
+        <v>381</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="25">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25">
+        <v>338</v>
+      </c>
+      <c r="G16" s="25">
+        <v>78</v>
+      </c>
+      <c r="H16" s="25">
+        <v>78</v>
+      </c>
+      <c r="I16" s="25">
+        <v>26</v>
+      </c>
+      <c r="J16" s="26">
+        <f>SUM(F16:I16)</f>
+        <v>520</v>
+      </c>
+      <c r="K16" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L16" s="26">
+        <f>J16*(1+K16)</f>
+        <v>650</v>
+      </c>
+      <c r="M16" s="26">
+        <f>E16*L16</f>
+        <v>650</v>
+      </c>
+      <c r="N16" s="24" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1">
+      <c r="A17" s="24" t="s">
+        <v>386</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="E17" s="25">
+        <v>1</v>
+      </c>
+      <c r="F17" s="25">
+        <v>156</v>
+      </c>
+      <c r="G17" s="25">
+        <v>36</v>
+      </c>
+      <c r="H17" s="25">
+        <v>36</v>
+      </c>
+      <c r="I17" s="25">
+        <v>12</v>
+      </c>
+      <c r="J17" s="26">
+        <f>SUM(F17:I17)</f>
+        <v>240</v>
+      </c>
+      <c r="K17" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L17" s="26">
+        <f>J17*(1+K17)</f>
+        <v>300</v>
+      </c>
+      <c r="M17" s="26">
+        <f>E17*L17</f>
+        <v>300</v>
+      </c>
+      <c r="N17" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1">
+      <c r="A18" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="E18" s="25">
+        <v>1</v>
+      </c>
+      <c r="F18" s="25">
+        <v>162</v>
+      </c>
+      <c r="G18" s="25">
+        <v>90</v>
+      </c>
+      <c r="H18" s="25">
+        <v>72</v>
+      </c>
+      <c r="I18" s="25">
+        <v>36</v>
+      </c>
+      <c r="J18" s="26">
+        <f>SUM(F18:I18)</f>
+        <v>360</v>
+      </c>
+      <c r="K18" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L18" s="26">
+        <f>J18*(1+K18)</f>
+        <v>450</v>
+      </c>
+      <c r="M18" s="26">
+        <f>E18*L18</f>
+        <v>450</v>
+      </c>
+      <c r="N18" s="24" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1">
+      <c r="A19" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="E19" s="25">
+        <v>1</v>
+      </c>
+      <c r="F19" s="25">
+        <v>30</v>
+      </c>
+      <c r="G19" s="25">
+        <v>110</v>
+      </c>
+      <c r="H19" s="25">
+        <v>40</v>
+      </c>
+      <c r="I19" s="25">
+        <v>20</v>
+      </c>
+      <c r="J19" s="26">
+        <f>SUM(F19:I19)</f>
+        <v>200</v>
+      </c>
+      <c r="K19" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L19" s="26">
+        <f>J19*(1+K19)</f>
+        <v>250</v>
+      </c>
+      <c r="M19" s="26">
+        <f>E19*L19</f>
+        <v>250</v>
+      </c>
+      <c r="N19" s="24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1">
+      <c r="A20" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="25">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="25">
+        <v>0.396</v>
+      </c>
+      <c r="G20" s="25">
+        <v>0.22</v>
+      </c>
+      <c r="H20" s="25">
+        <v>0.176</v>
+      </c>
+      <c r="I20" s="25">
+        <v>0.088</v>
+      </c>
+      <c r="J20" s="26">
+        <f>SUM(F20:I20)</f>
+        <v>0.88</v>
+      </c>
+      <c r="K20" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L20" s="26">
+        <f>J20*(1+K20)</f>
+        <v>1.1</v>
+      </c>
+      <c r="M20" s="26">
+        <f>E20*L20</f>
+        <v>1100</v>
+      </c>
+      <c r="N20" s="24" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1">
+      <c r="A21" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="E21" s="25">
+        <v>1</v>
+      </c>
+      <c r="F21" s="25">
+        <v>162</v>
+      </c>
+      <c r="G21" s="25">
+        <v>90</v>
+      </c>
+      <c r="H21" s="25">
+        <v>72</v>
+      </c>
+      <c r="I21" s="25">
+        <v>36</v>
+      </c>
+      <c r="J21" s="26">
+        <f>SUM(F21:I21)</f>
+        <v>360</v>
+      </c>
+      <c r="K21" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L21" s="26">
+        <f>J21*(1+K21)</f>
+        <v>450</v>
+      </c>
+      <c r="M21" s="26">
+        <f>E21*L21</f>
+        <v>450</v>
+      </c>
+      <c r="N21" s="24" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1">
+      <c r="A22" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>412</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>413</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="E22" s="25">
+        <v>3</v>
+      </c>
+      <c r="F22" s="25">
+        <v>104</v>
+      </c>
+      <c r="G22" s="25">
+        <v>24</v>
+      </c>
+      <c r="H22" s="25">
+        <v>24</v>
+      </c>
+      <c r="I22" s="25">
+        <v>8</v>
+      </c>
+      <c r="J22" s="26">
+        <f>SUM(F22:I22)</f>
+        <v>160</v>
+      </c>
+      <c r="K22" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L22" s="26">
+        <f>J22*(1+K22)</f>
+        <v>200</v>
+      </c>
+      <c r="M22" s="26">
+        <f>E22*L22</f>
+        <v>600</v>
+      </c>
+      <c r="N22" s="24" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1">
+      <c r="A23" s="24" t="s">
+        <v>416</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="E23" s="25">
+        <v>1</v>
+      </c>
+      <c r="F23" s="25">
+        <v>156</v>
+      </c>
+      <c r="G23" s="25">
+        <v>36</v>
+      </c>
+      <c r="H23" s="25">
+        <v>36</v>
+      </c>
+      <c r="I23" s="25">
+        <v>12</v>
+      </c>
+      <c r="J23" s="26">
+        <f>SUM(F23:I23)</f>
+        <v>240</v>
+      </c>
+      <c r="K23" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L23" s="26">
+        <f>J23*(1+K23)</f>
+        <v>300</v>
+      </c>
+      <c r="M23" s="26">
+        <f>E23*L23</f>
+        <v>300</v>
+      </c>
+      <c r="N23" s="24" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1">
+      <c r="A24" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="E24" s="25">
+        <v>1</v>
+      </c>
+      <c r="F24" s="25">
+        <v>110</v>
+      </c>
+      <c r="G24" s="25">
+        <v>40</v>
+      </c>
+      <c r="H24" s="25">
+        <v>30</v>
+      </c>
+      <c r="I24" s="25">
+        <v>20</v>
+      </c>
+      <c r="J24" s="26">
+        <f>SUM(F24:I24)</f>
+        <v>200</v>
+      </c>
+      <c r="K24" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L24" s="26">
+        <f>J24*(1+K24)</f>
+        <v>250</v>
+      </c>
+      <c r="M24" s="26">
+        <f>E24*L24</f>
+        <v>250</v>
+      </c>
+      <c r="N24" s="24" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15" customHeight="1">
+      <c r="A25" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="E25" s="25">
+        <v>1</v>
+      </c>
+      <c r="F25" s="25">
+        <v>12</v>
+      </c>
+      <c r="G25" s="25">
+        <v>44</v>
+      </c>
+      <c r="H25" s="25">
+        <v>16</v>
+      </c>
+      <c r="I25" s="25">
+        <v>8</v>
+      </c>
+      <c r="J25" s="26">
+        <f>SUM(F25:I25)</f>
+        <v>80</v>
+      </c>
+      <c r="K25" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L25" s="26">
+        <f>J25*(1+K25)</f>
+        <v>100</v>
+      </c>
+      <c r="M25" s="26">
+        <f>E25*L25</f>
+        <v>100</v>
+      </c>
+      <c r="N25" s="24" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1">
+      <c r="A26" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="E26" s="25">
+        <v>12000</v>
+      </c>
+      <c r="F26" s="25">
+        <v>0.0528</v>
+      </c>
+      <c r="G26" s="25">
+        <v>0.0192</v>
+      </c>
+      <c r="H26" s="25">
+        <v>0.0144</v>
+      </c>
+      <c r="I26" s="25">
+        <v>0.0096</v>
+      </c>
+      <c r="J26" s="26">
+        <f>SUM(F26:I26)</f>
+        <v>0.09599999999999999</v>
+      </c>
+      <c r="K26" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L26" s="26">
+        <f>J26*(1+K26)</f>
+        <v>0.12</v>
+      </c>
+      <c r="M26" s="26">
+        <f>E26*L26</f>
+        <v>1440</v>
+      </c>
+      <c r="N26" s="24" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15" customHeight="1">
+      <c r="A27" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" s="25">
+        <v>6000</v>
+      </c>
+      <c r="F27" s="25">
+        <v>0.0792</v>
+      </c>
+      <c r="G27" s="25">
+        <v>0.0288</v>
+      </c>
+      <c r="H27" s="25">
+        <v>0.0216</v>
+      </c>
+      <c r="I27" s="25">
+        <v>0.0144</v>
+      </c>
+      <c r="J27" s="26">
+        <f>SUM(F27:I27)</f>
+        <v>0.14400000000000002</v>
+      </c>
+      <c r="K27" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L27" s="26">
+        <f>J27*(1+K27)</f>
+        <v>0.18</v>
+      </c>
+      <c r="M27" s="26">
+        <f>E27*L27</f>
+        <v>1080</v>
+      </c>
+      <c r="N27" s="24" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15" customHeight="1">
+      <c r="A28" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="E28" s="25">
+        <v>60</v>
+      </c>
+      <c r="F28" s="25">
+        <v>2.6</v>
+      </c>
+      <c r="G28" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="H28" s="25">
+        <v>0.6</v>
+      </c>
+      <c r="I28" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="J28" s="26">
+        <f>SUM(F28:I28)</f>
+        <v>4</v>
+      </c>
+      <c r="K28" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L28" s="26">
+        <f>J28*(1+K28)</f>
+        <v>5</v>
+      </c>
+      <c r="M28" s="26">
+        <f>E28*L28</f>
+        <v>300</v>
+      </c>
+      <c r="N28" s="24" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1">
+      <c r="A29" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="E29" s="25">
+        <v>2500</v>
+      </c>
+      <c r="F29" s="25">
+        <v>0.1408</v>
+      </c>
+      <c r="G29" s="25">
+        <v>0.0512</v>
+      </c>
+      <c r="H29" s="25">
+        <v>0.0384</v>
+      </c>
+      <c r="I29" s="25">
+        <v>0.0256</v>
+      </c>
+      <c r="J29" s="26">
+        <f>SUM(F29:I29)</f>
+        <v>0.256</v>
+      </c>
+      <c r="K29" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L29" s="26">
+        <f>J29*(1+K29)</f>
+        <v>0.32</v>
+      </c>
+      <c r="M29" s="26">
+        <f>E29*L29</f>
+        <v>800</v>
+      </c>
+      <c r="N29" s="24" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1">
+      <c r="A30" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="E30" s="25">
+        <v>2500</v>
+      </c>
+      <c r="F30" s="25">
+        <v>0.0832</v>
+      </c>
+      <c r="G30" s="25">
+        <v>0.0192</v>
+      </c>
+      <c r="H30" s="25">
+        <v>0.0192</v>
+      </c>
+      <c r="I30" s="25">
+        <v>0.0064</v>
+      </c>
+      <c r="J30" s="26">
+        <f>SUM(F30:I30)</f>
+        <v>0.12799999999999997</v>
+      </c>
+      <c r="K30" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L30" s="26">
+        <f>J30*(1+K30)</f>
+        <v>0.16</v>
+      </c>
+      <c r="M30" s="26">
+        <f>E30*L30</f>
+        <v>400</v>
+      </c>
+      <c r="N30" s="24" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" customHeight="1">
+      <c r="A31" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>458</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="E31" s="25">
+        <v>10</v>
+      </c>
+      <c r="F31" s="25">
+        <v>6.48</v>
+      </c>
+      <c r="G31" s="25">
+        <v>3.6</v>
+      </c>
+      <c r="H31" s="25">
+        <v>2.88</v>
+      </c>
+      <c r="I31" s="25">
+        <v>1.44</v>
+      </c>
+      <c r="J31" s="26">
+        <f>SUM(F31:I31)</f>
+        <v>14.4</v>
+      </c>
+      <c r="K31" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L31" s="26">
+        <f>J31*(1+K31)</f>
+        <v>18</v>
+      </c>
+      <c r="M31" s="26">
+        <f>E31*L31</f>
+        <v>180</v>
+      </c>
+      <c r="N31" s="24" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15" customHeight="1">
+      <c r="A32" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="E32" s="25">
+        <v>8000</v>
+      </c>
+      <c r="F32" s="25">
+        <v>0.066</v>
+      </c>
+      <c r="G32" s="25">
+        <v>0.024</v>
+      </c>
+      <c r="H32" s="25">
+        <v>0.018</v>
+      </c>
+      <c r="I32" s="25">
+        <v>0.012</v>
+      </c>
+      <c r="J32" s="26">
+        <f>SUM(F32:I32)</f>
+        <v>0.12</v>
+      </c>
+      <c r="K32" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L32" s="26">
+        <f>J32*(1+K32)</f>
+        <v>0.15</v>
+      </c>
+      <c r="M32" s="26">
+        <f>E32*L32</f>
+        <v>1200</v>
+      </c>
+      <c r="N32" s="24" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15" customHeight="1">
+      <c r="A33" s="24" t="s">
+        <v>466</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="E33" s="25">
+        <v>80</v>
+      </c>
+      <c r="F33" s="25">
+        <v>1.44</v>
+      </c>
+      <c r="G33" s="25">
+        <v>0.8</v>
+      </c>
+      <c r="H33" s="25">
+        <v>0.64</v>
+      </c>
+      <c r="I33" s="25">
+        <v>0.32</v>
+      </c>
+      <c r="J33" s="26">
+        <f>SUM(F33:I33)</f>
+        <v>3.2</v>
+      </c>
+      <c r="K33" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L33" s="26">
+        <f>J33*(1+K33)</f>
+        <v>4</v>
+      </c>
+      <c r="M33" s="26">
+        <f>E33*L33</f>
+        <v>320</v>
+      </c>
+      <c r="N33" s="24" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15" customHeight="1">
+      <c r="A34" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="E34" s="25">
+        <v>1</v>
+      </c>
+      <c r="F34" s="25">
+        <v>180</v>
+      </c>
+      <c r="G34" s="25">
+        <v>100</v>
+      </c>
+      <c r="H34" s="25">
+        <v>80</v>
+      </c>
+      <c r="I34" s="25">
+        <v>40</v>
+      </c>
+      <c r="J34" s="26">
+        <f>SUM(F34:I34)</f>
+        <v>400</v>
+      </c>
+      <c r="K34" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L34" s="26">
+        <f>J34*(1+K34)</f>
+        <v>500</v>
+      </c>
+      <c r="M34" s="26">
+        <f>E34*L34</f>
+        <v>500</v>
+      </c>
+      <c r="N34" s="24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15" customHeight="1">
+      <c r="A35" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="E35" s="25">
+        <v>1</v>
+      </c>
+      <c r="F35" s="25">
+        <v>90</v>
+      </c>
+      <c r="G35" s="25">
+        <v>50</v>
+      </c>
+      <c r="H35" s="25">
+        <v>40</v>
+      </c>
+      <c r="I35" s="25">
+        <v>20</v>
+      </c>
+      <c r="J35" s="26">
+        <f>SUM(F35:I35)</f>
+        <v>200</v>
+      </c>
+      <c r="K35" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L35" s="26">
+        <f>J35*(1+K35)</f>
+        <v>250</v>
+      </c>
+      <c r="M35" s="26">
+        <f>E35*L35</f>
+        <v>250</v>
+      </c>
+      <c r="N35" s="24" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15" customHeight="1">
+      <c r="A36" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="E36" s="25">
+        <v>1</v>
+      </c>
+      <c r="F36" s="25">
+        <v>12.12</v>
+      </c>
+      <c r="G36" s="25">
+        <v>44.44</v>
+      </c>
+      <c r="H36" s="25">
+        <v>16.16</v>
+      </c>
+      <c r="I36" s="25">
+        <v>8.08</v>
+      </c>
+      <c r="J36" s="26">
+        <f>SUM(F36:I36)</f>
+        <v>80.8</v>
+      </c>
+      <c r="K36" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L36" s="26">
+        <f>J36*(1+K36)</f>
+        <v>101</v>
+      </c>
+      <c r="M36" s="26">
+        <f>E36*L36</f>
+        <v>101</v>
+      </c>
+      <c r="N36" s="24" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15" customHeight="1">
+      <c r="A37" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="E37" s="25">
+        <v>1</v>
+      </c>
+      <c r="F37" s="25">
+        <v>12</v>
+      </c>
+      <c r="G37" s="25">
+        <v>44</v>
+      </c>
+      <c r="H37" s="25">
+        <v>16</v>
+      </c>
+      <c r="I37" s="25">
+        <v>8</v>
+      </c>
+      <c r="J37" s="26">
+        <f>SUM(F37:I37)</f>
+        <v>80</v>
+      </c>
+      <c r="K37" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L37" s="26">
+        <f>J37*(1+K37)</f>
+        <v>100</v>
+      </c>
+      <c r="M37" s="26">
+        <f>E37*L37</f>
+        <v>100</v>
+      </c>
+      <c r="N37" s="24" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1">
+      <c r="A38" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="E38" s="25">
+        <v>1</v>
+      </c>
+      <c r="F38" s="25">
+        <v>48</v>
+      </c>
+      <c r="G38" s="25">
+        <v>176</v>
+      </c>
+      <c r="H38" s="25">
+        <v>64</v>
+      </c>
+      <c r="I38" s="25">
+        <v>32</v>
+      </c>
+      <c r="J38" s="26">
+        <f>SUM(F38:I38)</f>
+        <v>320</v>
+      </c>
+      <c r="K38" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L38" s="26">
+        <f>J38*(1+K38)</f>
+        <v>400</v>
+      </c>
+      <c r="M38" s="26">
+        <f>E38*L38</f>
+        <v>400</v>
+      </c>
+      <c r="N38" s="24" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15" customHeight="1">
+      <c r="A39" s="24" t="s">
+        <v>496</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>497</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>498</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="E39" s="25">
+        <v>25</v>
+      </c>
+      <c r="F39" s="25">
+        <v>3.12</v>
+      </c>
+      <c r="G39" s="25">
+        <v>11.44</v>
+      </c>
+      <c r="H39" s="25">
+        <v>4.16</v>
+      </c>
+      <c r="I39" s="25">
+        <v>2.08</v>
+      </c>
+      <c r="J39" s="26">
+        <f>SUM(F39:I39)</f>
+        <v>20.799999999999997</v>
+      </c>
+      <c r="K39" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L39" s="26">
+        <f>J39*(1+K39)</f>
+        <v>26</v>
+      </c>
+      <c r="M39" s="26">
+        <f>E39*L39</f>
+        <v>650</v>
+      </c>
+      <c r="N39" s="24" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15" customHeight="1">
+      <c r="A40" s="24" t="s">
+        <v>501</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>502</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>503</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>504</v>
+      </c>
+      <c r="E40" s="25">
+        <v>1</v>
+      </c>
+      <c r="F40" s="25">
+        <v>24</v>
+      </c>
+      <c r="G40" s="25">
+        <v>88</v>
+      </c>
+      <c r="H40" s="25">
+        <v>32</v>
+      </c>
+      <c r="I40" s="25">
+        <v>16</v>
+      </c>
+      <c r="J40" s="26">
+        <f>SUM(F40:I40)</f>
+        <v>160</v>
+      </c>
+      <c r="K40" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L40" s="26">
+        <f>J40*(1+K40)</f>
+        <v>200</v>
+      </c>
+      <c r="M40" s="26">
+        <f>E40*L40</f>
+        <v>200</v>
+      </c>
+      <c r="N40" s="24" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15" customHeight="1">
+      <c r="A41" s="24" t="s">
+        <v>506</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>507</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="E41" s="25">
+        <v>1</v>
+      </c>
+      <c r="F41" s="25">
+        <v>12</v>
+      </c>
+      <c r="G41" s="25">
+        <v>84</v>
+      </c>
+      <c r="H41" s="25">
+        <v>12</v>
+      </c>
+      <c r="I41" s="25">
+        <v>12</v>
+      </c>
+      <c r="J41" s="26">
+        <f>SUM(F41:I41)</f>
+        <v>120</v>
+      </c>
+      <c r="K41" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L41" s="26">
+        <f>J41*(1+K41)</f>
+        <v>150</v>
+      </c>
+      <c r="M41" s="26">
+        <f>E41*L41</f>
+        <v>150</v>
+      </c>
+      <c r="N41" s="24" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15" customHeight="1">
+      <c r="A42" s="24" t="s">
+        <v>511</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="E42" s="25">
+        <v>1</v>
+      </c>
+      <c r="F42" s="25">
+        <v>12</v>
+      </c>
+      <c r="G42" s="25">
+        <v>44</v>
+      </c>
+      <c r="H42" s="25">
+        <v>16</v>
+      </c>
+      <c r="I42" s="25">
+        <v>8</v>
+      </c>
+      <c r="J42" s="26">
+        <f>SUM(F42:I42)</f>
+        <v>80</v>
+      </c>
+      <c r="K42" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L42" s="26">
+        <f>J42*(1+K42)</f>
+        <v>100</v>
+      </c>
+      <c r="M42" s="26">
+        <f>E42*L42</f>
+        <v>100</v>
+      </c>
+      <c r="N42" s="24" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15" customHeight="1">
+      <c r="A43" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>518</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>519</v>
+      </c>
+      <c r="E43" s="25">
+        <v>1</v>
+      </c>
+      <c r="F43" s="25">
+        <v>24</v>
+      </c>
+      <c r="G43" s="25">
+        <v>88</v>
+      </c>
+      <c r="H43" s="25">
+        <v>32</v>
+      </c>
+      <c r="I43" s="25">
+        <v>16</v>
+      </c>
+      <c r="J43" s="26">
+        <f>SUM(F43:I43)</f>
+        <v>160</v>
+      </c>
+      <c r="K43" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L43" s="26">
+        <f>J43*(1+K43)</f>
+        <v>200</v>
+      </c>
+      <c r="M43" s="26">
+        <f>E43*L43</f>
+        <v>200</v>
+      </c>
+      <c r="N43" s="24" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15" customHeight="1">
+      <c r="A44" s="24" t="s">
+        <v>521</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>524</v>
+      </c>
+      <c r="E44" s="25">
+        <v>1</v>
+      </c>
+      <c r="F44" s="25">
+        <v>8</v>
+      </c>
+      <c r="G44" s="25">
+        <v>56</v>
+      </c>
+      <c r="H44" s="25">
+        <v>8</v>
+      </c>
+      <c r="I44" s="25">
+        <v>8</v>
+      </c>
+      <c r="J44" s="26">
+        <f>SUM(F44:I44)</f>
+        <v>80</v>
+      </c>
+      <c r="K44" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="L44" s="26">
+        <f>J44*(1+K44)</f>
+        <v>100</v>
+      </c>
+      <c r="M44" s="26">
+        <f>E44*L44</f>
+        <v>100</v>
+      </c>
+      <c r="N44" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15" customHeight="1">
+      <c r="A46" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="29">
+        <f>SUM(M3:M44)</f>
+        <v>19971</v>
+      </c>
+      <c r="N46" s="28" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="30" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1">
+      <c r="A49" t="s">
+        <v>529</v>
+      </c>
+      <c r="B49" s="31">
+        <f>SUMIF($B$3:$B$44,A49,$M$3:$M$44)</f>
         <v>2400</v>
       </c>
-      <c r="C3" s="9">
-        <f>B3/$B$9</f>
+      <c r="C49" s="32">
+        <f>B49/$M$46</f>
         <v>0.12017425266636624</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="D49" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1">
+      <c r="A50" t="s">
+        <v>531</v>
+      </c>
+      <c r="B50" s="31">
+        <f>SUMIF($B$3:$B$44,A50,$M$3:$M$44)</f>
         <v>6300</v>
       </c>
-      <c r="C4" s="9">
-        <f>B4/$B$9</f>
+      <c r="C50" s="32">
+        <f>B50/$M$46</f>
         <v>0.31545741324921134</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="D50" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1">
+      <c r="A51" t="s">
+        <v>533</v>
+      </c>
+      <c r="B51" s="31">
+        <f>SUMIF($B$3:$B$44,A51,$M$3:$M$44)</f>
         <v>2800</v>
       </c>
-      <c r="C5" s="9">
-        <f>B5/$B$9</f>
+      <c r="C51" s="32">
+        <f>B51/$M$46</f>
         <v>0.14020329477742727</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="D51" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1">
+      <c r="A52" t="s">
+        <v>535</v>
+      </c>
+      <c r="B52" s="31">
+        <f>SUMIF($B$3:$B$44,A52,$M$3:$M$44)</f>
         <v>4200</v>
       </c>
-      <c r="C6" s="9">
-        <f>B6/$B$9</f>
+      <c r="C52" s="32">
+        <f>B52/$M$46</f>
         <v>0.2103049421661409</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15">
-      <c r="A7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="D52" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1">
+      <c r="A53" t="s">
+        <v>537</v>
+      </c>
+      <c r="B53" s="31">
+        <f>SUMIF($B$3:$B$44,A53,$M$3:$M$44)</f>
         <v>2471</v>
       </c>
-      <c r="C7" s="9">
-        <f>B7/$B$9</f>
+      <c r="C53" s="32">
+        <f>B53/$M$46</f>
         <v>0.12372940764107956</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="D53" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1">
+      <c r="A54" t="s">
+        <v>539</v>
+      </c>
+      <c r="B54" s="31">
+        <f>SUMIF($B$3:$B$44,A54,$M$3:$M$44)</f>
         <v>1800</v>
       </c>
-      <c r="C8" s="9">
-        <f>B8/$B$9</f>
+      <c r="C54" s="32">
+        <f>B54/$M$46</f>
         <v>0.09013068949977468</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15">
-      <c r="A9" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="3">
-        <f>SUM(B3:B8)</f>
-        <v>19971</v>
-      </c>
-      <c r="C9" s="3">
-        <f>SUM(C3:C8)</f>
-        <v>1</v>
+      <c r="D54" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+  <autoFilter ref="A2:N44"/>
+  <mergeCells count="2">
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="landscape"/>
   <headerFooter>
-    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <oddFooter>&amp;CAPU referencial académico — no contractual&amp;RPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3467,147 +7908,453 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.00390625" style="0" customWidth="1"/>
-    <col min="2" max="2" width="16.00390625" style="0" customWidth="1"/>
-    <col min="3" max="3" width="18.00390625" style="0" customWidth="1"/>
-    <col min="4" max="4" width="16.00390625" style="0" customWidth="1"/>
-    <col min="5" max="5" width="28.00390625" style="0" customWidth="1"/>
+    <col min="1" max="1" width="28.00390625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="39.00390625" style="0" customWidth="1"/>
+    <col min="3" max="4" width="54.00390625" style="0" customWidth="1"/>
+    <col min="5" max="5" width="23.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3" s="10">
-        <f>Supuestos!B17</f>
-        <v>0.8</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3*Presupuesto!$B$9</f>
-        <v>15976.8</v>
-      </c>
-      <c r="D3" s="9">
-        <f>Supuestos!B20</f>
-        <v>0.09</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="10">
-        <f>Supuestos!B18</f>
-        <v>0.1</v>
-      </c>
-      <c r="C4" s="8">
-        <f>B4*Presupuesto!$B$9</f>
-        <v>1997.1</v>
-      </c>
-      <c r="D4" s="9">
-        <f>Supuestos!B21</f>
-        <v>0.11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="10">
-        <f>Supuestos!B19</f>
-        <v>0.1</v>
-      </c>
-      <c r="C5" s="8">
-        <f>B5*Presupuesto!$B$9</f>
-        <v>1997.1</v>
-      </c>
-      <c r="D5" s="9">
-        <f>Supuestos!B22</f>
-        <v>0.14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="10">
-        <f>SUM(B3:B5)</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <f>SUM(C3:C5)</f>
-        <v>19970.999999999996</v>
-      </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15">
-      <c r="A7" s="3"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="10">
-        <f>B3*D3+B4*D4*(1-Supuestos!$B$23)+B5*D5</f>
-        <v>0.09315</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="3"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1">
+      <c r="A3" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1">
+      <c r="A4" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1">
+      <c r="A6" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1">
+      <c r="A7" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1">
+      <c r="A8" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1">
+      <c r="A9" s="40" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1">
+      <c r="A10" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1">
+      <c r="A11" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1">
+      <c r="A12" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1">
+      <c r="A13" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1">
+      <c r="A14" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1">
+      <c r="A15" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="B15" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1">
+      <c r="A16" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1">
+      <c r="A17" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1">
+      <c r="A18" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1">
+      <c r="A19" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1">
+      <c r="A20" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1">
+      <c r="A21" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1">
+      <c r="A22" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1">
+      <c r="A23" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1">
+      <c r="A24" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1">
+      <c r="A25" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>293</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1">
+      <c r="A26" s="40" t="s">
+        <v>296</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>297</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E2"/>
+  <autoFilter ref="A2:E26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
-  </headerFooter>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="landscape"/>
 </worksheet>
 </file>
 
@@ -3616,693 +8363,130 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.00390625" style="0" customWidth="1"/>
+    <col min="1" max="1" width="62.00390625" style="0" customWidth="1"/>
     <col min="2" max="2" width="18.00390625" style="0" customWidth="1"/>
-    <col min="3" max="5" width="17.00390625" style="0" customWidth="1"/>
-    <col min="6" max="6" width="18.00390625" style="0" customWidth="1"/>
+    <col min="3" max="3" width="15.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A3,'APU Referencial'!$M$3:$M$44)</f>
+        <v>2400</v>
+      </c>
+      <c r="C3" s="9">
+        <f>B3/$B$9</f>
+        <v>0.12017425266636624</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A4,'APU Referencial'!$M$3:$M$44)</f>
+        <v>6300</v>
+      </c>
+      <c r="C4" s="9">
+        <f>B4/$B$9</f>
+        <v>0.31545741324921134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A5,'APU Referencial'!$M$3:$M$44)</f>
+        <v>2800</v>
+      </c>
+      <c r="C5" s="9">
+        <f>B5/$B$9</f>
+        <v>0.14020329477742727</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A6,'APU Referencial'!$M$3:$M$44)</f>
+        <v>4200</v>
+      </c>
+      <c r="C6" s="9">
+        <f>B6/$B$9</f>
+        <v>0.2103049421661409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" customHeight="1">
+      <c r="A7" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A7,'APU Referencial'!$M$3:$M$44)</f>
+        <v>2471</v>
+      </c>
+      <c r="C7" s="9">
+        <f>B7/$B$9</f>
+        <v>0.12372940764107956</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="6">
+        <f>SUMIF('APU Referencial'!$B$3:$B$44,A8,'APU Referencial'!$M$3:$M$44)</f>
+        <v>1800</v>
+      </c>
+      <c r="C8" s="9">
+        <f>B8/$B$9</f>
+        <v>0.09013068949977468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" customHeight="1">
+      <c r="A9" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="21">
+        <f>SUM(B3:B8)</f>
+        <v>19971</v>
+      </c>
+      <c r="C9" s="21">
+        <f>SUM(C3:C8)</f>
         <v>1</v>
       </c>
-      <c r="B3" s="8">
-        <f>Financiacion!$C$4</f>
-        <v>1997.1</v>
-      </c>
-      <c r="C3" s="8">
-        <f>IF(A3&lt;=Supuestos!$B$24,B3*Supuestos!$B$21,0)</f>
-        <v>219.681</v>
-      </c>
-      <c r="D3" s="8">
-        <f>IF(A3&lt;=Supuestos!$B$24,MIN(B3,E3-C3),0)</f>
-        <v>119.42943005639776</v>
-      </c>
-      <c r="E3" s="8">
-        <f>IF(A3&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F3" s="8">
-        <f>MAX(0,B3-D3)</f>
-        <v>1877.6705699436022</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="3">
-        <f>A3+1</f>
-        <v>2</v>
-      </c>
-      <c r="B4" s="8">
-        <f>F3</f>
-        <v>1877.6705699436022</v>
-      </c>
-      <c r="C4" s="8">
-        <f>IF(A4&lt;=Supuestos!$B$24,B4*Supuestos!$B$21,0)</f>
-        <v>206.543762693796</v>
-      </c>
-      <c r="D4" s="8">
-        <f>IF(A4&lt;=Supuestos!$B$24,MIN(B4,E4-C4),0)</f>
-        <v>132.56666736260178</v>
-      </c>
-      <c r="E4" s="8">
-        <f>IF(A4&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F4" s="8">
-        <f>MAX(0,B4-D4)</f>
-        <v>1745.1039025810005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="3">
-        <f>A4+1</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="8">
-        <f>F4</f>
-        <v>1745.1039025810005</v>
-      </c>
-      <c r="C5" s="8">
-        <f>IF(A5&lt;=Supuestos!$B$24,B5*Supuestos!$B$21,0)</f>
-        <v>191.96142928391</v>
-      </c>
-      <c r="D5" s="8">
-        <f>IF(A5&lt;=Supuestos!$B$24,MIN(B5,E5-C5),0)</f>
-        <v>147.14900077248777</v>
-      </c>
-      <c r="E5" s="8">
-        <f>IF(A5&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F5" s="8">
-        <f>MAX(0,B5-D5)</f>
-        <v>1597.9549018085127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="3">
-        <f>A5+1</f>
-        <v>4</v>
-      </c>
-      <c r="B6" s="8">
-        <f>F5</f>
-        <v>1597.9549018085127</v>
-      </c>
-      <c r="C6" s="8">
-        <f>IF(A6&lt;=Supuestos!$B$24,B6*Supuestos!$B$21,0)</f>
-        <v>175.775039198936</v>
-      </c>
-      <c r="D6" s="8">
-        <f>IF(A6&lt;=Supuestos!$B$24,MIN(B6,E6-C6),0)</f>
-        <v>163.33539085746176</v>
-      </c>
-      <c r="E6" s="8">
-        <f>IF(A6&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F6" s="8">
-        <f>MAX(0,B6-D6)</f>
-        <v>1434.6195109510509</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="3">
-        <f>A6+1</f>
-        <v>5</v>
-      </c>
-      <c r="B7" s="8">
-        <f>F6</f>
-        <v>1434.6195109510509</v>
-      </c>
-      <c r="C7" s="8">
-        <f>IF(A7&lt;=Supuestos!$B$24,B7*Supuestos!$B$21,0)</f>
-        <v>157.808146204616</v>
-      </c>
-      <c r="D7" s="8">
-        <f>IF(A7&lt;=Supuestos!$B$24,MIN(B7,E7-C7),0)</f>
-        <v>181.30228385178177</v>
-      </c>
-      <c r="E7" s="8">
-        <f>IF(A7&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F7" s="8">
-        <f>MAX(0,B7-D7)</f>
-        <v>1253.317227099269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="3">
-        <f>A7+1</f>
-        <v>6</v>
-      </c>
-      <c r="B8" s="8">
-        <f>F7</f>
-        <v>1253.317227099269</v>
-      </c>
-      <c r="C8" s="8">
-        <f>IF(A8&lt;=Supuestos!$B$24,B8*Supuestos!$B$21,0)</f>
-        <v>137.86489498092</v>
-      </c>
-      <c r="D8" s="8">
-        <f>IF(A8&lt;=Supuestos!$B$24,MIN(B8,E8-C8),0)</f>
-        <v>201.24553507547776</v>
-      </c>
-      <c r="E8" s="8">
-        <f>IF(A8&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F8" s="8">
-        <f>MAX(0,B8-D8)</f>
-        <v>1052.0716920237912</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="3">
-        <f>A8+1</f>
-        <v>7</v>
-      </c>
-      <c r="B9" s="8">
-        <f>F8</f>
-        <v>1052.0716920237912</v>
-      </c>
-      <c r="C9" s="8">
-        <f>IF(A9&lt;=Supuestos!$B$24,B9*Supuestos!$B$21,0)</f>
-        <v>115.727886122617</v>
-      </c>
-      <c r="D9" s="8">
-        <f>IF(A9&lt;=Supuestos!$B$24,MIN(B9,E9-C9),0)</f>
-        <v>223.38254393378077</v>
-      </c>
-      <c r="E9" s="8">
-        <f>IF(A9&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F9" s="8">
-        <f>MAX(0,B9-D9)</f>
-        <v>828.6891480900105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="3">
-        <f>A9+1</f>
-        <v>8</v>
-      </c>
-      <c r="B10" s="8">
-        <f>F9</f>
-        <v>828.6891480900105</v>
-      </c>
-      <c r="C10" s="8">
-        <f>IF(A10&lt;=Supuestos!$B$24,B10*Supuestos!$B$21,0)</f>
-        <v>91.1558062899012</v>
-      </c>
-      <c r="D10" s="8">
-        <f>IF(A10&lt;=Supuestos!$B$24,MIN(B10,E10-C10),0)</f>
-        <v>247.95462376649658</v>
-      </c>
-      <c r="E10" s="8">
-        <f>IF(A10&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F10" s="8">
-        <f>MAX(0,B10-D10)</f>
-        <v>580.7345243235138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="3">
-        <f>A10+1</f>
-        <v>9</v>
-      </c>
-      <c r="B11" s="8">
-        <f>F10</f>
-        <v>580.7345243235138</v>
-      </c>
-      <c r="C11" s="8">
-        <f>IF(A11&lt;=Supuestos!$B$24,B11*Supuestos!$B$21,0)</f>
-        <v>63.8807976755865</v>
-      </c>
-      <c r="D11" s="8">
-        <f>IF(A11&lt;=Supuestos!$B$24,MIN(B11,E11-C11),0)</f>
-        <v>275.22963238081127</v>
-      </c>
-      <c r="E11" s="8">
-        <f>IF(A11&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F11" s="8">
-        <f>MAX(0,B11-D11)</f>
-        <v>305.50489194270256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="3">
-        <f>A11+1</f>
-        <v>10</v>
-      </c>
-      <c r="B12" s="8">
-        <f>F11</f>
-        <v>305.50489194270256</v>
-      </c>
-      <c r="C12" s="8">
-        <f>IF(A12&lt;=Supuestos!$B$24,B12*Supuestos!$B$21,0)</f>
-        <v>33.6055381136973</v>
-      </c>
-      <c r="D12" s="8">
-        <f>IF(A12&lt;=Supuestos!$B$24,MIN(B12,E12-C12),0)</f>
-        <v>305.50489194270045</v>
-      </c>
-      <c r="E12" s="8">
-        <f>IF(A12&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>339.1104300563978</v>
-      </c>
-      <c r="F12" s="8">
-        <f>MAX(0,B12-D12)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="3">
-        <f>A12+1</f>
-        <v>11</v>
-      </c>
-      <c r="B13" s="8">
-        <f>F12</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C13" s="8">
-        <f>IF(A13&lt;=Supuestos!$B$24,B13*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <f>IF(A13&lt;=Supuestos!$B$24,MIN(B13,E13-C13),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <f>IF(A13&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <f>MAX(0,B13-D13)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="3">
-        <f>A13+1</f>
-        <v>12</v>
-      </c>
-      <c r="B14" s="8">
-        <f>F13</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C14" s="8">
-        <f>IF(A14&lt;=Supuestos!$B$24,B14*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="8">
-        <f>IF(A14&lt;=Supuestos!$B$24,MIN(B14,E14-C14),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
-        <f>IF(A14&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <f>MAX(0,B14-D14)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="3">
-        <f>A14+1</f>
-        <v>13</v>
-      </c>
-      <c r="B15" s="8">
-        <f>F14</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C15" s="8">
-        <f>IF(A15&lt;=Supuestos!$B$24,B15*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <f>IF(A15&lt;=Supuestos!$B$24,MIN(B15,E15-C15),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <f>IF(A15&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="8">
-        <f>MAX(0,B15-D15)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="3">
-        <f>A15+1</f>
-        <v>14</v>
-      </c>
-      <c r="B16" s="8">
-        <f>F15</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C16" s="8">
-        <f>IF(A16&lt;=Supuestos!$B$24,B16*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="8">
-        <f>IF(A16&lt;=Supuestos!$B$24,MIN(B16,E16-C16),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="8">
-        <f>IF(A16&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="8">
-        <f>MAX(0,B16-D16)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="3">
-        <f>A16+1</f>
-        <v>15</v>
-      </c>
-      <c r="B17" s="8">
-        <f>F16</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C17" s="8">
-        <f>IF(A17&lt;=Supuestos!$B$24,B17*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <f>IF(A17&lt;=Supuestos!$B$24,MIN(B17,E17-C17),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="8">
-        <f>IF(A17&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <f>MAX(0,B17-D17)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="3">
-        <f>A17+1</f>
-        <v>16</v>
-      </c>
-      <c r="B18" s="8">
-        <f>F17</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C18" s="8">
-        <f>IF(A18&lt;=Supuestos!$B$24,B18*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="8">
-        <f>IF(A18&lt;=Supuestos!$B$24,MIN(B18,E18-C18),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
-        <f>IF(A18&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <f>MAX(0,B18-D18)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="3">
-        <f>A18+1</f>
-        <v>17</v>
-      </c>
-      <c r="B19" s="8">
-        <f>F18</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C19" s="8">
-        <f>IF(A19&lt;=Supuestos!$B$24,B19*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="8">
-        <f>IF(A19&lt;=Supuestos!$B$24,MIN(B19,E19-C19),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <f>IF(A19&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="8">
-        <f>MAX(0,B19-D19)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="3">
-        <f>A19+1</f>
-        <v>18</v>
-      </c>
-      <c r="B20" s="8">
-        <f>F19</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C20" s="8">
-        <f>IF(A20&lt;=Supuestos!$B$24,B20*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="8">
-        <f>IF(A20&lt;=Supuestos!$B$24,MIN(B20,E20-C20),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="8">
-        <f>IF(A20&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="8">
-        <f>MAX(0,B20-D20)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="3">
-        <f>A20+1</f>
-        <v>19</v>
-      </c>
-      <c r="B21" s="8">
-        <f>F20</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C21" s="8">
-        <f>IF(A21&lt;=Supuestos!$B$24,B21*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <f>IF(A21&lt;=Supuestos!$B$24,MIN(B21,E21-C21),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="8">
-        <f>IF(A21&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <f>MAX(0,B21-D21)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="3">
-        <f>A21+1</f>
-        <v>20</v>
-      </c>
-      <c r="B22" s="8">
-        <f>F21</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C22" s="8">
-        <f>IF(A22&lt;=Supuestos!$B$24,B22*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="8">
-        <f>IF(A22&lt;=Supuestos!$B$24,MIN(B22,E22-C22),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
-        <f>IF(A22&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="8">
-        <f>MAX(0,B22-D22)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="3">
-        <f>A22+1</f>
-        <v>21</v>
-      </c>
-      <c r="B23" s="8">
-        <f>F22</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C23" s="8">
-        <f>IF(A23&lt;=Supuestos!$B$24,B23*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="8">
-        <f>IF(A23&lt;=Supuestos!$B$24,MIN(B23,E23-C23),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
-        <f>IF(A23&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="8">
-        <f>MAX(0,B23-D23)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="3">
-        <f>A23+1</f>
-        <v>22</v>
-      </c>
-      <c r="B24" s="8">
-        <f>F23</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C24" s="8">
-        <f>IF(A24&lt;=Supuestos!$B$24,B24*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="8">
-        <f>IF(A24&lt;=Supuestos!$B$24,MIN(B24,E24-C24),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
-        <f>IF(A24&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <f>MAX(0,B24-D24)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="3">
-        <f>A24+1</f>
-        <v>23</v>
-      </c>
-      <c r="B25" s="8">
-        <f>F24</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C25" s="8">
-        <f>IF(A25&lt;=Supuestos!$B$24,B25*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
-        <f>IF(A25&lt;=Supuestos!$B$24,MIN(B25,E25-C25),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
-        <f>IF(A25&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <f>MAX(0,B25-D25)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="3">
-        <f>A25+1</f>
-        <v>24</v>
-      </c>
-      <c r="B26" s="8">
-        <f>F25</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C26" s="8">
-        <f>IF(A26&lt;=Supuestos!$B$24,B26*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="8">
-        <f>IF(A26&lt;=Supuestos!$B$24,MIN(B26,E26-C26),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <f>IF(A26&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="8">
-        <f>MAX(0,B26-D26)</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="3">
-        <f>A26+1</f>
-        <v>25</v>
-      </c>
-      <c r="B27" s="8">
-        <f>F26</f>
-        <v>2.1032064978498966E-12</v>
-      </c>
-      <c r="C27" s="8">
-        <f>IF(A27&lt;=Supuestos!$B$24,B27*Supuestos!$B$21,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="8">
-        <f>IF(A27&lt;=Supuestos!$B$24,MIN(B27,E27-C27),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="8">
-        <f>IF(A27&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="8">
-        <f>MAX(0,B27-D27)</f>
-        <v>2.1032064978498966E-12</v>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F2"/>
+  <autoFilter ref="A2:C2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4318,6 +8502,857 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="35.00390625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="16.00390625" style="0" customWidth="1"/>
+    <col min="3" max="3" width="18.00390625" style="0" customWidth="1"/>
+    <col min="4" max="4" width="16.00390625" style="0" customWidth="1"/>
+    <col min="5" max="5" width="28.00390625" style="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1">
+      <c r="A3" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="10">
+        <f>Supuestos!B17</f>
+        <v>0.8</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3*Presupuesto!$B$9</f>
+        <v>15976.8</v>
+      </c>
+      <c r="D3" s="9">
+        <f>Supuestos!B20</f>
+        <v>0.09</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1">
+      <c r="A4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="10">
+        <f>Supuestos!B18</f>
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="8">
+        <f>B4*Presupuesto!$B$9</f>
+        <v>1997.1</v>
+      </c>
+      <c r="D4" s="9">
+        <f>Supuestos!B21</f>
+        <v>0.11</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="10">
+        <f>Supuestos!B19</f>
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="8">
+        <f>B5*Presupuesto!$B$9</f>
+        <v>1997.1</v>
+      </c>
+      <c r="D5" s="9">
+        <f>Supuestos!B22</f>
+        <v>0.14</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="10">
+        <f>SUM(B3:B5)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <f>SUM(C3:C5)</f>
+        <v>19970.999999999996</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1">
+      <c r="A7" s="21"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1">
+      <c r="A8" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="10">
+        <f>B3*D3+B4*D4*(1-Supuestos!$B$23)+B5*D5</f>
+        <v>0.09315</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="21"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.00390625" style="0" customWidth="1"/>
+    <col min="2" max="2" width="18.00390625" style="0" customWidth="1"/>
+    <col min="3" max="5" width="17.00390625" style="0" customWidth="1"/>
+    <col min="6" max="6" width="18.00390625" style="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1">
+      <c r="A3" s="21">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <f>Financiacion!$C$4</f>
+        <v>1997.1</v>
+      </c>
+      <c r="C3" s="8">
+        <f>IF(A3&lt;=Supuestos!$B$24,B3*Supuestos!$B$21,0)</f>
+        <v>219.681</v>
+      </c>
+      <c r="D3" s="8">
+        <f>IF(A3&lt;=Supuestos!$B$24,MIN(B3,E3-C3),0)</f>
+        <v>119.42943005639776</v>
+      </c>
+      <c r="E3" s="8">
+        <f>IF(A3&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F3" s="8">
+        <f>MAX(0,B3-D3)</f>
+        <v>1877.6705699436022</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1">
+      <c r="A4" s="21">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="8">
+        <f>F3</f>
+        <v>1877.6705699436022</v>
+      </c>
+      <c r="C4" s="8">
+        <f>IF(A4&lt;=Supuestos!$B$24,B4*Supuestos!$B$21,0)</f>
+        <v>206.543762693796</v>
+      </c>
+      <c r="D4" s="8">
+        <f>IF(A4&lt;=Supuestos!$B$24,MIN(B4,E4-C4),0)</f>
+        <v>132.56666736260178</v>
+      </c>
+      <c r="E4" s="8">
+        <f>IF(A4&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F4" s="8">
+        <f>MAX(0,B4-D4)</f>
+        <v>1745.1039025810005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1">
+      <c r="A5" s="21">
+        <f>A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="8">
+        <f>F4</f>
+        <v>1745.1039025810005</v>
+      </c>
+      <c r="C5" s="8">
+        <f>IF(A5&lt;=Supuestos!$B$24,B5*Supuestos!$B$21,0)</f>
+        <v>191.96142928391</v>
+      </c>
+      <c r="D5" s="8">
+        <f>IF(A5&lt;=Supuestos!$B$24,MIN(B5,E5-C5),0)</f>
+        <v>147.14900077248777</v>
+      </c>
+      <c r="E5" s="8">
+        <f>IF(A5&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F5" s="8">
+        <f>MAX(0,B5-D5)</f>
+        <v>1597.9549018085127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1">
+      <c r="A6" s="21">
+        <f>A5+1</f>
+        <v>4</v>
+      </c>
+      <c r="B6" s="8">
+        <f>F5</f>
+        <v>1597.9549018085127</v>
+      </c>
+      <c r="C6" s="8">
+        <f>IF(A6&lt;=Supuestos!$B$24,B6*Supuestos!$B$21,0)</f>
+        <v>175.775039198936</v>
+      </c>
+      <c r="D6" s="8">
+        <f>IF(A6&lt;=Supuestos!$B$24,MIN(B6,E6-C6),0)</f>
+        <v>163.33539085746176</v>
+      </c>
+      <c r="E6" s="8">
+        <f>IF(A6&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F6" s="8">
+        <f>MAX(0,B6-D6)</f>
+        <v>1434.6195109510509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1">
+      <c r="A7" s="21">
+        <f>A6+1</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="8">
+        <f>F6</f>
+        <v>1434.6195109510509</v>
+      </c>
+      <c r="C7" s="8">
+        <f>IF(A7&lt;=Supuestos!$B$24,B7*Supuestos!$B$21,0)</f>
+        <v>157.808146204616</v>
+      </c>
+      <c r="D7" s="8">
+        <f>IF(A7&lt;=Supuestos!$B$24,MIN(B7,E7-C7),0)</f>
+        <v>181.30228385178177</v>
+      </c>
+      <c r="E7" s="8">
+        <f>IF(A7&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F7" s="8">
+        <f>MAX(0,B7-D7)</f>
+        <v>1253.317227099269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1">
+      <c r="A8" s="21">
+        <f>A7+1</f>
+        <v>6</v>
+      </c>
+      <c r="B8" s="8">
+        <f>F7</f>
+        <v>1253.317227099269</v>
+      </c>
+      <c r="C8" s="8">
+        <f>IF(A8&lt;=Supuestos!$B$24,B8*Supuestos!$B$21,0)</f>
+        <v>137.86489498092</v>
+      </c>
+      <c r="D8" s="8">
+        <f>IF(A8&lt;=Supuestos!$B$24,MIN(B8,E8-C8),0)</f>
+        <v>201.24553507547776</v>
+      </c>
+      <c r="E8" s="8">
+        <f>IF(A8&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F8" s="8">
+        <f>MAX(0,B8-D8)</f>
+        <v>1052.0716920237912</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1">
+      <c r="A9" s="21">
+        <f>A8+1</f>
+        <v>7</v>
+      </c>
+      <c r="B9" s="8">
+        <f>F8</f>
+        <v>1052.0716920237912</v>
+      </c>
+      <c r="C9" s="8">
+        <f>IF(A9&lt;=Supuestos!$B$24,B9*Supuestos!$B$21,0)</f>
+        <v>115.727886122617</v>
+      </c>
+      <c r="D9" s="8">
+        <f>IF(A9&lt;=Supuestos!$B$24,MIN(B9,E9-C9),0)</f>
+        <v>223.38254393378077</v>
+      </c>
+      <c r="E9" s="8">
+        <f>IF(A9&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F9" s="8">
+        <f>MAX(0,B9-D9)</f>
+        <v>828.6891480900105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1">
+      <c r="A10" s="21">
+        <f>A9+1</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="8">
+        <f>F9</f>
+        <v>828.6891480900105</v>
+      </c>
+      <c r="C10" s="8">
+        <f>IF(A10&lt;=Supuestos!$B$24,B10*Supuestos!$B$21,0)</f>
+        <v>91.1558062899012</v>
+      </c>
+      <c r="D10" s="8">
+        <f>IF(A10&lt;=Supuestos!$B$24,MIN(B10,E10-C10),0)</f>
+        <v>247.95462376649658</v>
+      </c>
+      <c r="E10" s="8">
+        <f>IF(A10&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F10" s="8">
+        <f>MAX(0,B10-D10)</f>
+        <v>580.7345243235138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1">
+      <c r="A11" s="21">
+        <f>A10+1</f>
+        <v>9</v>
+      </c>
+      <c r="B11" s="8">
+        <f>F10</f>
+        <v>580.7345243235138</v>
+      </c>
+      <c r="C11" s="8">
+        <f>IF(A11&lt;=Supuestos!$B$24,B11*Supuestos!$B$21,0)</f>
+        <v>63.8807976755865</v>
+      </c>
+      <c r="D11" s="8">
+        <f>IF(A11&lt;=Supuestos!$B$24,MIN(B11,E11-C11),0)</f>
+        <v>275.22963238081127</v>
+      </c>
+      <c r="E11" s="8">
+        <f>IF(A11&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F11" s="8">
+        <f>MAX(0,B11-D11)</f>
+        <v>305.50489194270256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1">
+      <c r="A12" s="21">
+        <f>A11+1</f>
+        <v>10</v>
+      </c>
+      <c r="B12" s="8">
+        <f>F11</f>
+        <v>305.50489194270256</v>
+      </c>
+      <c r="C12" s="8">
+        <f>IF(A12&lt;=Supuestos!$B$24,B12*Supuestos!$B$21,0)</f>
+        <v>33.6055381136973</v>
+      </c>
+      <c r="D12" s="8">
+        <f>IF(A12&lt;=Supuestos!$B$24,MIN(B12,E12-C12),0)</f>
+        <v>305.50489194270045</v>
+      </c>
+      <c r="E12" s="8">
+        <f>IF(A12&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>339.1104300563978</v>
+      </c>
+      <c r="F12" s="8">
+        <f>MAX(0,B12-D12)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1">
+      <c r="A13" s="21">
+        <f>A12+1</f>
+        <v>11</v>
+      </c>
+      <c r="B13" s="8">
+        <f>F12</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C13" s="8">
+        <f>IF(A13&lt;=Supuestos!$B$24,B13*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <f>IF(A13&lt;=Supuestos!$B$24,MIN(B13,E13-C13),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <f>IF(A13&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <f>MAX(0,B13-D13)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1">
+      <c r="A14" s="21">
+        <f>A13+1</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="8">
+        <f>F13</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C14" s="8">
+        <f>IF(A14&lt;=Supuestos!$B$24,B14*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <f>IF(A14&lt;=Supuestos!$B$24,MIN(B14,E14-C14),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <f>IF(A14&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="8">
+        <f>MAX(0,B14-D14)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1">
+      <c r="A15" s="21">
+        <f>A14+1</f>
+        <v>13</v>
+      </c>
+      <c r="B15" s="8">
+        <f>F14</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C15" s="8">
+        <f>IF(A15&lt;=Supuestos!$B$24,B15*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <f>IF(A15&lt;=Supuestos!$B$24,MIN(B15,E15-C15),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <f>IF(A15&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <f>MAX(0,B15-D15)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1">
+      <c r="A16" s="21">
+        <f>A15+1</f>
+        <v>14</v>
+      </c>
+      <c r="B16" s="8">
+        <f>F15</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C16" s="8">
+        <f>IF(A16&lt;=Supuestos!$B$24,B16*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <f>IF(A16&lt;=Supuestos!$B$24,MIN(B16,E16-C16),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="8">
+        <f>IF(A16&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="8">
+        <f>MAX(0,B16-D16)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1">
+      <c r="A17" s="21">
+        <f>A16+1</f>
+        <v>15</v>
+      </c>
+      <c r="B17" s="8">
+        <f>F16</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C17" s="8">
+        <f>IF(A17&lt;=Supuestos!$B$24,B17*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <f>IF(A17&lt;=Supuestos!$B$24,MIN(B17,E17-C17),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <f>IF(A17&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <f>MAX(0,B17-D17)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1">
+      <c r="A18" s="21">
+        <f>A17+1</f>
+        <v>16</v>
+      </c>
+      <c r="B18" s="8">
+        <f>F17</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C18" s="8">
+        <f>IF(A18&lt;=Supuestos!$B$24,B18*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <f>IF(A18&lt;=Supuestos!$B$24,MIN(B18,E18-C18),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <f>IF(A18&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <f>MAX(0,B18-D18)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1">
+      <c r="A19" s="21">
+        <f>A18+1</f>
+        <v>17</v>
+      </c>
+      <c r="B19" s="8">
+        <f>F18</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C19" s="8">
+        <f>IF(A19&lt;=Supuestos!$B$24,B19*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <f>IF(A19&lt;=Supuestos!$B$24,MIN(B19,E19-C19),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <f>IF(A19&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <f>MAX(0,B19-D19)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1">
+      <c r="A20" s="21">
+        <f>A19+1</f>
+        <v>18</v>
+      </c>
+      <c r="B20" s="8">
+        <f>F19</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C20" s="8">
+        <f>IF(A20&lt;=Supuestos!$B$24,B20*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <f>IF(A20&lt;=Supuestos!$B$24,MIN(B20,E20-C20),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="8">
+        <f>IF(A20&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="8">
+        <f>MAX(0,B20-D20)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1">
+      <c r="A21" s="21">
+        <f>A20+1</f>
+        <v>19</v>
+      </c>
+      <c r="B21" s="8">
+        <f>F20</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C21" s="8">
+        <f>IF(A21&lt;=Supuestos!$B$24,B21*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <f>IF(A21&lt;=Supuestos!$B$24,MIN(B21,E21-C21),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <f>IF(A21&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <f>MAX(0,B21-D21)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1">
+      <c r="A22" s="21">
+        <f>A21+1</f>
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
+        <f>F21</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C22" s="8">
+        <f>IF(A22&lt;=Supuestos!$B$24,B22*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <f>IF(A22&lt;=Supuestos!$B$24,MIN(B22,E22-C22),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <f>IF(A22&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="8">
+        <f>MAX(0,B22-D22)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1">
+      <c r="A23" s="21">
+        <f>A22+1</f>
+        <v>21</v>
+      </c>
+      <c r="B23" s="8">
+        <f>F22</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C23" s="8">
+        <f>IF(A23&lt;=Supuestos!$B$24,B23*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <f>IF(A23&lt;=Supuestos!$B$24,MIN(B23,E23-C23),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>IF(A23&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <f>MAX(0,B23-D23)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" customHeight="1">
+      <c r="A24" s="21">
+        <f>A23+1</f>
+        <v>22</v>
+      </c>
+      <c r="B24" s="8">
+        <f>F23</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C24" s="8">
+        <f>IF(A24&lt;=Supuestos!$B$24,B24*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <f>IF(A24&lt;=Supuestos!$B$24,MIN(B24,E24-C24),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <f>IF(A24&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <f>MAX(0,B24-D24)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" customHeight="1">
+      <c r="A25" s="21">
+        <f>A24+1</f>
+        <v>23</v>
+      </c>
+      <c r="B25" s="8">
+        <f>F24</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C25" s="8">
+        <f>IF(A25&lt;=Supuestos!$B$24,B25*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <f>IF(A25&lt;=Supuestos!$B$24,MIN(B25,E25-C25),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <f>IF(A25&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <f>MAX(0,B25-D25)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1">
+      <c r="A26" s="21">
+        <f>A25+1</f>
+        <v>24</v>
+      </c>
+      <c r="B26" s="8">
+        <f>F25</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C26" s="8">
+        <f>IF(A26&lt;=Supuestos!$B$24,B26*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <f>IF(A26&lt;=Supuestos!$B$24,MIN(B26,E26-C26),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <f>IF(A26&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f>MAX(0,B26-D26)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" customHeight="1">
+      <c r="A27" s="21">
+        <f>A26+1</f>
+        <v>25</v>
+      </c>
+      <c r="B27" s="8">
+        <f>F26</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+      <c r="C27" s="8">
+        <f>IF(A27&lt;=Supuestos!$B$24,B27*Supuestos!$B$21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <f>IF(A27&lt;=Supuestos!$B$24,MIN(B27,E27-C27),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="8">
+        <f>IF(A27&lt;=Supuestos!$B$24,-PMT(Supuestos!$B$21,Supuestos!$B$24,Financiacion!$C$4),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="8">
+        <f>MAX(0,B27-D27)</f>
+        <v>2.1032064978498966E-12</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -4325,62 +9360,62 @@
     <col min="2" max="16" width="13.00390625" style="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:16" ht="15" customHeight="1">
+      <c r="A2" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="33" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15">
+    <row r="3" spans="1:16" ht="15" customHeight="1">
       <c r="A3" s="11">
         <v>0</v>
       </c>
@@ -4435,7 +9470,7 @@
         <v>-19971</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15">
+    <row r="4" spans="1:16" ht="15" customHeight="1">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -4500,7 +9535,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15">
+    <row r="5" spans="1:16" ht="15" customHeight="1">
       <c r="A5" s="11">
         <f>A4+1</f>
         <v>2</v>
@@ -4566,7 +9601,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15">
+    <row r="6" spans="1:16" ht="15" customHeight="1">
       <c r="A6" s="11">
         <f>A5+1</f>
         <v>3</v>
@@ -4632,7 +9667,7 @@
         <v>3213.6749999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15">
+    <row r="7" spans="1:16" ht="15" customHeight="1">
       <c r="A7" s="11">
         <f>A6+1</f>
         <v>4</v>
@@ -4698,7 +9733,7 @@
         <v>3326.153625</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15">
+    <row r="8" spans="1:16" ht="15" customHeight="1">
       <c r="A8" s="11">
         <f>A7+1</f>
         <v>5</v>
@@ -4764,7 +9799,7 @@
         <v>3442.569001875</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15">
+    <row r="9" spans="1:16" ht="15" customHeight="1">
       <c r="A9" s="11">
         <f>A8+1</f>
         <v>6</v>
@@ -4830,7 +9865,7 @@
         <v>3563.05891694062</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15">
+    <row r="10" spans="1:16" ht="15" customHeight="1">
       <c r="A10" s="11">
         <f>A9+1</f>
         <v>7</v>
@@ -4896,7 +9931,7 @@
         <v>3687.76597903355</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15">
+    <row r="11" spans="1:16" ht="15" customHeight="1">
       <c r="A11" s="11">
         <f>A10+1</f>
         <v>8</v>
@@ -4962,7 +9997,7 @@
         <v>3816.8377882997193</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15">
+    <row r="12" spans="1:16" ht="15" customHeight="1">
       <c r="A12" s="11">
         <f>A11+1</f>
         <v>9</v>
@@ -5028,7 +10063,7 @@
         <v>3950.4271108902103</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15">
+    <row r="13" spans="1:16" ht="15" customHeight="1">
       <c r="A13" s="11">
         <f>A12+1</f>
         <v>10</v>
@@ -5094,7 +10129,7 @@
         <v>4088.6920597713697</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15">
+    <row r="14" spans="1:16" ht="15" customHeight="1">
       <c r="A14" s="11">
         <f>A13+1</f>
         <v>11</v>
@@ -5160,7 +10195,7 @@
         <v>4231.7962818633605</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15">
+    <row r="15" spans="1:16" ht="15" customHeight="1">
       <c r="A15" s="11">
         <f>A14+1</f>
         <v>12</v>
@@ -5226,7 +10261,7 @@
         <v>4379.90915172858</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15">
+    <row r="16" spans="1:16" ht="15" customHeight="1">
       <c r="A16" s="11">
         <f>A15+1</f>
         <v>13</v>
@@ -5292,7 +10327,7 @@
         <v>4533.205972039091</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15">
+    <row r="17" spans="1:16" ht="15" customHeight="1">
       <c r="A17" s="11">
         <f>A16+1</f>
         <v>14</v>
@@ -5358,7 +10393,7 @@
         <v>4691.86818106044</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15">
+    <row r="18" spans="1:16" ht="15" customHeight="1">
       <c r="A18" s="11">
         <f>A17+1</f>
         <v>15</v>
@@ -5424,7 +10459,7 @@
         <v>4856.08356739757</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15">
+    <row r="19" spans="1:16" ht="15" customHeight="1">
       <c r="A19" s="11">
         <f>A18+1</f>
         <v>16</v>
@@ -5490,7 +10525,7 @@
         <v>5026.046492256481</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15">
+    <row r="20" spans="1:16" ht="15" customHeight="1">
       <c r="A20" s="11">
         <f>A19+1</f>
         <v>17</v>
@@ -5556,7 +10591,7 @@
         <v>5201.958119485451</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15">
+    <row r="21" spans="1:16" ht="15" customHeight="1">
       <c r="A21" s="11">
         <f>A20+1</f>
         <v>18</v>
@@ -5622,7 +10657,7 @@
         <v>5384.02665366745</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15">
+    <row r="22" spans="1:16" ht="15" customHeight="1">
       <c r="A22" s="11">
         <f>A21+1</f>
         <v>19</v>
@@ -5688,7 +10723,7 @@
         <v>5572.467586545799</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15">
+    <row r="23" spans="1:16" ht="15" customHeight="1">
       <c r="A23" s="11">
         <f>A22+1</f>
         <v>20</v>
@@ -5754,7 +10789,7 @@
         <v>5767.503952074911</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15">
+    <row r="24" spans="1:16" ht="15" customHeight="1">
       <c r="A24" s="11">
         <f>A23+1</f>
         <v>21</v>
@@ -5820,7 +10855,7 @@
         <v>5969.366590397529</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15">
+    <row r="25" spans="1:16" ht="15" customHeight="1">
       <c r="A25" s="11">
         <f>A24+1</f>
         <v>22</v>
@@ -5886,7 +10921,7 @@
         <v>6178.29442106144</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15">
+    <row r="26" spans="1:16" ht="15" customHeight="1">
       <c r="A26" s="11">
         <f>A25+1</f>
         <v>23</v>
@@ -5952,7 +10987,7 @@
         <v>6394.53472579859</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15">
+    <row r="27" spans="1:16" ht="15" customHeight="1">
       <c r="A27" s="11">
         <f>A26+1</f>
         <v>24</v>
@@ -6018,7 +11053,7 @@
         <v>6618.343441201541</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15">
+    <row r="28" spans="1:16" ht="15" customHeight="1">
       <c r="A28" s="11">
         <f>A27+1</f>
         <v>25</v>
@@ -6096,1081 +11131,4 @@
     <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AF8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="32" width="13.00390625" style="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
-        <v>2</v>
-      </c>
-      <c r="J2" s="5">
-        <v>3</v>
-      </c>
-      <c r="K2" s="5">
-        <v>4</v>
-      </c>
-      <c r="L2" s="5">
-        <v>5</v>
-      </c>
-      <c r="M2" s="5">
-        <v>6</v>
-      </c>
-      <c r="N2" s="5">
-        <v>7</v>
-      </c>
-      <c r="O2" s="5">
-        <v>8</v>
-      </c>
-      <c r="P2" s="5">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>10</v>
-      </c>
-      <c r="R2" s="5">
-        <v>11</v>
-      </c>
-      <c r="S2" s="5">
-        <v>12</v>
-      </c>
-      <c r="T2" s="5">
-        <v>13</v>
-      </c>
-      <c r="U2" s="5">
-        <v>14</v>
-      </c>
-      <c r="V2" s="5">
-        <v>15</v>
-      </c>
-      <c r="W2" s="5">
-        <v>16</v>
-      </c>
-      <c r="X2" s="5">
-        <v>17</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>18</v>
-      </c>
-      <c r="Z2" s="5">
-        <v>19</v>
-      </c>
-      <c r="AA2" s="5">
-        <v>20</v>
-      </c>
-      <c r="AB2" s="5">
-        <v>21</v>
-      </c>
-      <c r="AC2" s="5">
-        <v>22</v>
-      </c>
-      <c r="AD2" s="5">
-        <v>23</v>
-      </c>
-      <c r="AE2" s="5">
-        <v>24</v>
-      </c>
-      <c r="AF2" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" ht="15">
-      <c r="A3" s="13">
-        <v>0</v>
-      </c>
-      <c r="B3" s="14">
-        <f>(1-A3)/2*Presupuesto!$B$9</f>
-        <v>9985.5</v>
-      </c>
-      <c r="C3" s="14">
-        <f>(1-A3)/2*Presupuesto!$B$9</f>
-        <v>9985.5</v>
-      </c>
-      <c r="D3" s="15">
-        <f>IRR(G3:AF3)</f>
-        <v>-0.05397940689416905</v>
-      </c>
-      <c r="E3" s="14">
-        <f>NPV(Supuestos!$B$22,H3:AF3)+G3</f>
-        <v>-15794.058409020663</v>
-      </c>
-      <c r="F3" s="14" t="str">
-        <f>IF(D3&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-      <c r="G3" s="14">
-        <f>-C3</f>
-        <v>-9985.5</v>
-      </c>
-      <c r="H3" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1345.5521502819893</v>
-      </c>
-      <c r="I3" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1333.3021502819888</v>
-      </c>
-      <c r="J3" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1320.6234002819888</v>
-      </c>
-      <c r="K3" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1307.500894031989</v>
-      </c>
-      <c r="L3" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1293.919100063239</v>
-      </c>
-      <c r="M3" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1279.8619433055892</v>
-      </c>
-      <c r="N3" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1265.3127860614088</v>
-      </c>
-      <c r="O3" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1250.2544083136877</v>
-      </c>
-      <c r="P3" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1234.6689873447986</v>
-      </c>
-      <c r="Q3" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-1218.538076642001</v>
-      </c>
-      <c r="R3" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S3" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T3" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U3" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V3" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W3" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X3" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y3" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z3" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA3" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB3" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC3" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD3" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE3" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF3" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B3/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B3/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B3/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="15">
-      <c r="A4" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="B4" s="14">
-        <f>(1-A4)/2*Presupuesto!$B$9</f>
-        <v>5991.3</v>
-      </c>
-      <c r="C4" s="14">
-        <f>(1-A4)/2*Presupuesto!$B$9</f>
-        <v>5991.3</v>
-      </c>
-      <c r="D4" s="15">
-        <f>IRR(G4:AF4)</f>
-        <v>-0.014606345852164413</v>
-      </c>
-      <c r="E4" s="14">
-        <f>NPV(Supuestos!$B$22,H4:AF4)+G4</f>
-        <v>-8262.179968943623</v>
-      </c>
-      <c r="F4" s="14" t="str">
-        <f>IF(D4&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-      <c r="G4" s="14">
-        <f>-C4</f>
-        <v>-5991.3</v>
-      </c>
-      <c r="H4" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-667.3312901691934</v>
-      </c>
-      <c r="I4" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-655.0812901691934</v>
-      </c>
-      <c r="J4" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-642.4025401691933</v>
-      </c>
-      <c r="K4" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-629.2800339191958</v>
-      </c>
-      <c r="L4" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-615.6982399504434</v>
-      </c>
-      <c r="M4" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-601.6410831927935</v>
-      </c>
-      <c r="N4" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-587.0919259486129</v>
-      </c>
-      <c r="O4" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-572.0335482008929</v>
-      </c>
-      <c r="P4" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-556.4481272320008</v>
-      </c>
-      <c r="Q4" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-540.3172165292027</v>
-      </c>
-      <c r="R4" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S4" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T4" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U4" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V4" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W4" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X4" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y4" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z4" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA4" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB4" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC4" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD4" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE4" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF4" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B4/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B4/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B4/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="15">
-      <c r="A5" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="B5" s="14">
-        <f>(1-A5)/2*Presupuesto!$B$9</f>
-        <v>3994.2</v>
-      </c>
-      <c r="C5" s="14">
-        <f>(1-A5)/2*Presupuesto!$B$9</f>
-        <v>3994.2</v>
-      </c>
-      <c r="D5" s="15">
-        <f>IRR(G5:AF5)</f>
-        <v>0.021826211162366136</v>
-      </c>
-      <c r="E5" s="14">
-        <f>NPV(Supuestos!$B$22,H5:AF5)+G5</f>
-        <v>-4496.240748905102</v>
-      </c>
-      <c r="F5" s="14" t="str">
-        <f>IF(D5&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-      <c r="G5" s="14">
-        <f>-C5</f>
-        <v>-3994.2</v>
-      </c>
-      <c r="H5" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-328.22086011279555</v>
-      </c>
-      <c r="I5" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-315.9708601127956</v>
-      </c>
-      <c r="J5" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-303.292110112796</v>
-      </c>
-      <c r="K5" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-290.1696038627955</v>
-      </c>
-      <c r="L5" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-276.58780989404556</v>
-      </c>
-      <c r="M5" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-262.53065313639576</v>
-      </c>
-      <c r="N5" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-247.98149589221558</v>
-      </c>
-      <c r="O5" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-232.92311814449505</v>
-      </c>
-      <c r="P5" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-217.33769717560762</v>
-      </c>
-      <c r="Q5" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-201.2067864728034</v>
-      </c>
-      <c r="R5" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S5" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T5" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U5" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V5" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W5" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X5" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y5" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z5" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA5" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB5" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC5" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD5" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE5" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF5" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B5/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B5/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B5/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="15">
-      <c r="A6" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="B6" s="14">
-        <f>(1-A6)/2*Presupuesto!$B$9</f>
-        <v>2995.65</v>
-      </c>
-      <c r="C6" s="14">
-        <f>(1-A6)/2*Presupuesto!$B$9</f>
-        <v>2995.65</v>
-      </c>
-      <c r="D6" s="15">
-        <f>IRR(G6:AF6)</f>
-        <v>0.05203632439827555</v>
-      </c>
-      <c r="E6" s="14">
-        <f>NPV(Supuestos!$B$22,H6:AF6)+G6</f>
-        <v>-2613.271138885842</v>
-      </c>
-      <c r="F6" s="14" t="str">
-        <f>IF(D6&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-      <c r="G6" s="14">
-        <f>-C6</f>
-        <v>-2995.65</v>
-      </c>
-      <c r="H6" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-158.66564508459672</v>
-      </c>
-      <c r="I6" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-146.41564508459666</v>
-      </c>
-      <c r="J6" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-133.73689508459665</v>
-      </c>
-      <c r="K6" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-120.61438883459664</v>
-      </c>
-      <c r="L6" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-107.0325948658467</v>
-      </c>
-      <c r="M6" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-92.97543810819684</v>
-      </c>
-      <c r="N6" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-78.42628086401669</v>
-      </c>
-      <c r="O6" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-63.36790311629716</v>
-      </c>
-      <c r="P6" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-47.782482147406654</v>
-      </c>
-      <c r="Q6" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>-31.65157144460659</v>
-      </c>
-      <c r="R6" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S6" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T6" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U6" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V6" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W6" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X6" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y6" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z6" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA6" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB6" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC6" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD6" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE6" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF6" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B6/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B6/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B6/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" ht="15">
-      <c r="A7" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="B7" s="14">
-        <f>(1-A7)/2*Presupuesto!$B$9</f>
-        <v>1997.1</v>
-      </c>
-      <c r="C7" s="14">
-        <f>(1-A7)/2*Presupuesto!$B$9</f>
-        <v>1997.1</v>
-      </c>
-      <c r="D7" s="15">
-        <f>IRR(G7:AF7)</f>
-        <v>0.1046108925530724</v>
-      </c>
-      <c r="E7" s="14">
-        <f>NPV(Supuestos!$B$22,H7:AF7)+G7</f>
-        <v>-730.3015288665811</v>
-      </c>
-      <c r="F7" s="14" t="str">
-        <f>IF(D7&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-      <c r="G7" s="14">
-        <f>-C7</f>
-        <v>-1997.1</v>
-      </c>
-      <c r="H7" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>10.889569943602211</v>
-      </c>
-      <c r="I7" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>23.139569943602197</v>
-      </c>
-      <c r="J7" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>35.81831994360223</v>
-      </c>
-      <c r="K7" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>48.94082619360228</v>
-      </c>
-      <c r="L7" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>62.52262016235218</v>
-      </c>
-      <c r="M7" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>76.57977692000202</v>
-      </c>
-      <c r="N7" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>91.12893416418223</v>
-      </c>
-      <c r="O7" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>106.18731191190221</v>
-      </c>
-      <c r="P7" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>121.77273288079226</v>
-      </c>
-      <c r="Q7" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>137.90364358359233</v>
-      </c>
-      <c r="R7" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S7" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T7" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U7" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V7" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W7" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X7" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y7" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z7" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA7" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB7" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC7" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD7" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE7" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF7" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B7/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B7/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B7/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" ht="15">
-      <c r="A8" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="B8" s="14">
-        <f>(1-A8)/2*Presupuesto!$B$9</f>
-        <v>998.55</v>
-      </c>
-      <c r="C8" s="14">
-        <f>(1-A8)/2*Presupuesto!$B$9</f>
-        <v>998.55</v>
-      </c>
-      <c r="D8" s="15">
-        <f>IRR(G8:AF8)</f>
-        <v>0.2517685608889223</v>
-      </c>
-      <c r="E8" s="14">
-        <f>NPV(Supuestos!$B$22,H8:AF8)+G8</f>
-        <v>1152.6680811526796</v>
-      </c>
-      <c r="F8" s="14" t="str">
-        <f>IF(D8&gt;=Supuestos!$B$22,"Viable","No viable")</f>
-        <v>Viable</v>
-      </c>
-      <c r="G8" s="14">
-        <f>-C8</f>
-        <v>-998.55</v>
-      </c>
-      <c r="H8" s="14">
-        <f>'Flujos de Caja'!D4-('Amortizacion Deuda'!C3*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D3*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F4-('Amortizacion Deuda'!C3*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>180.44478497180108</v>
-      </c>
-      <c r="I8" s="14">
-        <f>'Flujos de Caja'!D5-('Amortizacion Deuda'!C4*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D4*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F5-('Amortizacion Deuda'!C4*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>192.6947849718011</v>
-      </c>
-      <c r="J8" s="14">
-        <f>'Flujos de Caja'!D6-('Amortizacion Deuda'!C5*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D5*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F6-('Amortizacion Deuda'!C5*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>205.37353497180118</v>
-      </c>
-      <c r="K8" s="14">
-        <f>'Flujos de Caja'!D7-('Amortizacion Deuda'!C6*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D6*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F7-('Amortizacion Deuda'!C6*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>218.4960412218012</v>
-      </c>
-      <c r="L8" s="14">
-        <f>'Flujos de Caja'!D8-('Amortizacion Deuda'!C7*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D7*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F8-('Amortizacion Deuda'!C7*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>232.07783519055107</v>
-      </c>
-      <c r="M8" s="14">
-        <f>'Flujos de Caja'!D9-('Amortizacion Deuda'!C8*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D8*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F9-('Amortizacion Deuda'!C8*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>246.13499194820096</v>
-      </c>
-      <c r="N8" s="14">
-        <f>'Flujos de Caja'!D10-('Amortizacion Deuda'!C9*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D9*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F10-('Amortizacion Deuda'!C9*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>260.6841491923811</v>
-      </c>
-      <c r="O8" s="14">
-        <f>'Flujos de Caja'!D11-('Amortizacion Deuda'!C10*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D10*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F11-('Amortizacion Deuda'!C10*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>275.7425269401012</v>
-      </c>
-      <c r="P8" s="14">
-        <f>'Flujos de Caja'!D12-('Amortizacion Deuda'!C11*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D11*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F12-('Amortizacion Deuda'!C11*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>291.32794790899123</v>
-      </c>
-      <c r="Q8" s="14">
-        <f>'Flujos de Caja'!D13-('Amortizacion Deuda'!C12*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D12*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F13-('Amortizacion Deuda'!C12*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>307.458858611791</v>
-      </c>
-      <c r="R8" s="14">
-        <f>'Flujos de Caja'!D14-('Amortizacion Deuda'!C13*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D13*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F14-('Amortizacion Deuda'!C13*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>493.7095662173897</v>
-      </c>
-      <c r="S8" s="14">
-        <f>'Flujos de Caja'!D15-('Amortizacion Deuda'!C14*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D14*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F15-('Amortizacion Deuda'!C14*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>510.9894010349999</v>
-      </c>
-      <c r="T8" s="14">
-        <f>'Flujos de Caja'!D16-('Amortizacion Deuda'!C15*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D15*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F16-('Amortizacion Deuda'!C15*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>528.87403007123</v>
-      </c>
-      <c r="U8" s="14">
-        <f>'Flujos de Caja'!D17-('Amortizacion Deuda'!C16*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D16*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F17-('Amortizacion Deuda'!C16*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>547.3846211237101</v>
-      </c>
-      <c r="V8" s="14">
-        <f>'Flujos de Caja'!D18-('Amortizacion Deuda'!C17*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D17*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F18-('Amortizacion Deuda'!C17*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>566.5430828630499</v>
-      </c>
-      <c r="W8" s="14">
-        <f>'Flujos de Caja'!D19-('Amortizacion Deuda'!C18*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D18*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F19-('Amortizacion Deuda'!C18*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>586.3720907632598</v>
-      </c>
-      <c r="X8" s="14">
-        <f>'Flujos de Caja'!D20-('Amortizacion Deuda'!C19*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D19*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F20-('Amortizacion Deuda'!C19*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>606.8951139399701</v>
-      </c>
-      <c r="Y8" s="14">
-        <f>'Flujos de Caja'!D21-('Amortizacion Deuda'!C20*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D20*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F21-('Amortizacion Deuda'!C20*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>628.1364429278701</v>
-      </c>
-      <c r="Z8" s="14">
-        <f>'Flujos de Caja'!D22-('Amortizacion Deuda'!C21*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D21*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F22-('Amortizacion Deuda'!C21*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>650.1212184303399</v>
-      </c>
-      <c r="AA8" s="14">
-        <f>'Flujos de Caja'!D23-('Amortizacion Deuda'!C22*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D22*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F23-('Amortizacion Deuda'!C22*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>672.8754610753999</v>
-      </c>
-      <c r="AB8" s="14">
-        <f>'Flujos de Caja'!D24-('Amortizacion Deuda'!C23*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D23*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F24-('Amortizacion Deuda'!C23*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>696.4261022130399</v>
-      </c>
-      <c r="AC8" s="14">
-        <f>'Flujos de Caja'!D25-('Amortizacion Deuda'!C24*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D24*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F25-('Amortizacion Deuda'!C24*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>720.8010157904996</v>
-      </c>
-      <c r="AD8" s="14">
-        <f>'Flujos de Caja'!D26-('Amortizacion Deuda'!C25*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D25*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F26-('Amortizacion Deuda'!C25*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>746.0290513431701</v>
-      </c>
-      <c r="AE8" s="14">
-        <f>'Flujos de Caja'!D27-('Amortizacion Deuda'!C26*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D26*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F27-('Amortizacion Deuda'!C26*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>772.1400681401801</v>
-      </c>
-      <c r="AF8" s="14">
-        <f>'Flujos de Caja'!D28-('Amortizacion Deuda'!C27*B8/Financiacion!$C$4)-('Amortizacion Deuda'!D27*B8/Financiacion!$C$4)-MAX(0,'Flujos de Caja'!F28-('Amortizacion Deuda'!C27*B8/Financiacion!$C$4))*Supuestos!$B$23</f>
-        <v>799.0512308413083</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:AF2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AF1"/>
-  </mergeCells>
-  <printOptions/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="landscape"/>
-  <headerFooter>
-    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.00390625" style="0" customWidth="1"/>
-    <col min="2" max="2" width="20.00390625" style="0" customWidth="1"/>
-    <col min="3" max="3" width="24.00390625" style="0" customWidth="1"/>
-    <col min="4" max="4" width="27.00390625" style="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15">
-      <c r="A1" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15">
-      <c r="A2" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="10">
-        <f>Financiacion!B8</f>
-        <v>0.09315</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15">
-      <c r="A4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="8">
-        <f>NPV(B3,'Flujos de Caja'!L4:L28)+'Flujos de Caja'!L3</f>
-        <v>-15486.829598504228</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="3" t="str">
-        <f>IF(B4&gt;0,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="10">
-        <f>IRR('Flujos de Caja'!L3:L28)</f>
-        <v>-0.024525933826823654</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <f>IF(B5&gt;B3,"Viable","No viable")</f>
-        <v>No viable</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="8">
-        <f>NPV(Supuestos!B22,'Flujos de Caja'!M4:M28)+'Flujos de Caja'!M3</f>
-        <v>-730.3015288665811</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="3" t="str">
-        <f>IF(B6&gt;0,"Viable","No alcanza Ke")</f>
-        <v>No alcanza Ke</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="10">
-        <f>IRR('Flujos de Caja'!M3:M28)</f>
-        <v>0.10461089255307242</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="3" t="str">
-        <f>IF(B7&gt;Supuestos!B22,"Viable","No alcanza Ke")</f>
-        <v>No alcanza Ke</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="8">
-        <f>NPV(Supuestos!B25,'Flujos de Caja'!P4:P28)+'Flujos de Caja'!P3</f>
-        <v>19625.705143047235</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="3" t="str">
-        <f>IF(B8&gt;0,"Viable","No viable")</f>
-        <v>Viable</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="3">
-        <f>NPV(Supuestos!B25,'Flujos de Caja'!O4:O28)/(Presupuesto!B9+NPV(Supuestos!B25,'Flujos de Caja'!C4:C28))</f>
-        <v>1.5583457184604053</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="3" t="str">
-        <f>IF(B9&gt;1,"Viable","No viable")</f>
-        <v>Viable</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15">
-      <c r="A10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="10">
-        <f>IRR('Flujos de Caja'!N3:N28)</f>
-        <v>0.10999999999958883</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="3" t="str">
-        <f>IF(ABS(B10-Supuestos!B21)&lt;0.000001,"Concilia","Revisar")</f>
-        <v>Concilia</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <printOptions/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="600" verticalDpi="600" orientation="portrait"/>
-  <headerFooter>
-    <oddFooter>&amp;RPágina &amp;P de &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>